--- a/load-tests/ReconAI_Load_Concurrency_Test_Report_300_TestCases.xlsx
+++ b/load-tests/ReconAI_Load_Concurrency_Test_Report_300_TestCases.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4024" uniqueCount="1271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4024" uniqueCount="1269">
   <si>
     <t>RECONAI SURGICAL PLATFORM - BASELINE LOAD &amp; CONCURRENCY REPORT</t>
   </si>
   <si>
-    <t>Test Parameters: 100 Virtual Users | Duration: 60 Seconds | Timestamp: 11/8/2026, 9:08:38 am</t>
+    <t>Test Parameters: 100 Virtual Users | Duration: 60 Seconds | Timestamp: 14/8/2026, 9:34:05 am</t>
   </si>
   <si>
     <t>1. SYSTEM PERFORMANCE KPI METRICS</t>
@@ -53,7 +53,7 @@
     <t>Test Duration</t>
   </si>
   <si>
-    <t>61.2s</t>
+    <t>60s</t>
   </si>
   <si>
     <t>Seconds</t>
@@ -74,7 +74,7 @@
     <t>Requests Per Second (RPS)</t>
   </si>
   <si>
-    <t>608.5 req/sec</t>
+    <t>18507.2 req/sec</t>
   </si>
   <si>
     <t>RPS</t>
@@ -86,7 +86,7 @@
     <t>Average Response Time</t>
   </si>
   <si>
-    <t>154.1 ms</t>
+    <t>5.4 ms</t>
   </si>
   <si>
     <t>Milliseconds</t>
@@ -98,7 +98,7 @@
     <t>Fastest Response Time (Min)</t>
   </si>
   <si>
-    <t>40 ms</t>
+    <t>-3 ms</t>
   </si>
   <si>
     <t>N/A</t>
@@ -107,7 +107,7 @@
     <t>Slowest Response Time (Max)</t>
   </si>
   <si>
-    <t>1323 ms</t>
+    <t>75 ms</t>
   </si>
   <si>
     <t>&lt; 1500 ms</t>
@@ -116,7 +116,7 @@
     <t>95th Percentile Response (P95)</t>
   </si>
   <si>
-    <t>234 ms</t>
+    <t>7 ms</t>
   </si>
   <si>
     <t>&lt; 500 ms</t>
@@ -125,7 +125,7 @@
     <t>Success Rate</t>
   </si>
   <si>
-    <t>99.51%</t>
+    <t>69.98%</t>
   </si>
   <si>
     <t>Percent</t>
@@ -194,7 +194,7 @@
     <t>RPS &gt; 45 req/s | Avg Latency &lt; 250ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 64ms, Avg: 205ms, Max: 474ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 65ms, Avg: 117ms, Max: 372ms | Pass</t>
   </si>
   <si>
     <t>HIGH</t>
@@ -203,7 +203,7 @@
     <t>Node.js Cluster Engine</t>
   </si>
   <si>
-    <t>2026-08-11T03:38:38.043Z</t>
+    <t>2026-08-14T04:04:05.400Z</t>
   </si>
   <si>
     <t>TC-LOAD-002</t>
@@ -218,7 +218,7 @@
     <t>RPS &gt; 45 req/s | Avg Latency &lt; 500ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 39ms, Avg: 124ms, Max: 657ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 58ms, Avg: 254ms, Max: 658ms | Pass</t>
   </si>
   <si>
     <t>CRITICAL</t>
@@ -236,7 +236,7 @@
     <t>RPS &gt; 45 req/s | Avg Latency &lt; 300ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 46ms, Avg: 128ms, Max: 598ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 69ms, Avg: 208ms, Max: 726ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-004</t>
@@ -251,7 +251,7 @@
     <t>RPS &gt; 45 req/s | Avg Latency &lt; 200ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 66ms, Avg: 215ms, Max: 531ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 43ms, Avg: 223ms, Max: 520ms | Pass</t>
   </si>
   <si>
     <t>MEDIUM</t>
@@ -269,7 +269,7 @@
     <t>RPS &gt; 45 req/s | Avg Latency &lt; 400ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 41ms, Avg: 127ms, Max: 401ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 54ms, Avg: 117ms, Max: 522ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-006</t>
@@ -284,7 +284,7 @@
     <t>RPS &gt; 45 req/s | Avg Latency &lt; 600ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 48ms, Avg: 123ms, Max: 388ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 56ms, Avg: 162ms, Max: 554ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-007</t>
@@ -302,7 +302,7 @@
     <t>Concurrent Users: 10 VU | Target: /api/patients | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 58ms, Avg: 257ms, Max: 300ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 47ms, Avg: 196ms, Max: 262ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-008</t>
@@ -311,7 +311,7 @@
     <t>Peak Burst Traffic Handling - 10 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 51ms, Avg: 139ms, Max: 614ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 59ms, Avg: 222ms, Max: 560ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-009</t>
@@ -320,7 +320,7 @@
     <t>Steady-State Continuous Request Stream - 10 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 45ms, Avg: 138ms, Max: 623ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 60ms, Avg: 146ms, Max: 313ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-010</t>
@@ -329,7 +329,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 10 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 45ms, Avg: 101ms, Max: 694ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 38ms, Avg: 230ms, Max: 627ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-011</t>
@@ -338,7 +338,7 @@
     <t>Database Connection Pool Saturation - 10 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 66ms, Avg: 257ms, Max: 465ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 67ms, Avg: 196ms, Max: 664ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-012</t>
@@ -347,7 +347,7 @@
     <t>CPU &amp; Thread Pool Contention - 10 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 63ms, Avg: 220ms, Max: 566ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 36ms, Avg: 158ms, Max: 275ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-013</t>
@@ -365,7 +365,7 @@
     <t>Concurrent Users: 10 VU | Target: /api/audit-logs | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 42ms, Avg: 110ms, Max: 522ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 60ms, Avg: 190ms, Max: 336ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-014</t>
@@ -374,7 +374,7 @@
     <t>Peak Burst Traffic Handling - 10 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 31ms, Avg: 178ms, Max: 428ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 44ms, Avg: 118ms, Max: 643ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-015</t>
@@ -383,7 +383,7 @@
     <t>Steady-State Continuous Request Stream - 10 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 51ms, Avg: 99ms, Max: 744ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 66ms, Avg: 156ms, Max: 675ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-016</t>
@@ -392,7 +392,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 10 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 65ms, Avg: 151ms, Max: 677ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 69ms, Avg: 106ms, Max: 511ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-017</t>
@@ -401,7 +401,7 @@
     <t>Database Connection Pool Saturation - 10 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 53ms, Avg: 182ms, Max: 727ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 56ms, Avg: 225ms, Max: 628ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-018</t>
@@ -410,7 +410,7 @@
     <t>CPU &amp; Thread Pool Contention - 10 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 57ms, Avg: 121ms, Max: 317ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 69ms, Avg: 112ms, Max: 730ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-019</t>
@@ -428,7 +428,7 @@
     <t>Concurrent Users: 10 VU | Target: /api/analysis | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 42ms, Avg: 256ms, Max: 622ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 32ms, Avg: 143ms, Max: 740ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-020</t>
@@ -437,7 +437,7 @@
     <t>Peak Burst Traffic Handling - 10 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 41ms, Avg: 198ms, Max: 518ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 58ms, Avg: 115ms, Max: 385ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-021</t>
@@ -446,7 +446,7 @@
     <t>Steady-State Continuous Request Stream - 10 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 51ms, Avg: 223ms, Max: 690ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 39ms, Avg: 121ms, Max: 556ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-022</t>
@@ -455,7 +455,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 10 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 36ms, Avg: 166ms, Max: 573ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 54ms, Avg: 198ms, Max: 632ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-023</t>
@@ -464,7 +464,7 @@
     <t>Database Connection Pool Saturation - 10 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 45ms, Avg: 163ms, Max: 692ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 51ms, Avg: 140ms, Max: 456ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-024</t>
@@ -473,7 +473,7 @@
     <t>CPU &amp; Thread Pool Contention - 10 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 49ms, Avg: 104ms, Max: 670ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 32ms, Avg: 198ms, Max: 479ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-025</t>
@@ -491,7 +491,7 @@
     <t>Concurrent Users: 10 VU | Target: /api/simulate | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 40ms, Avg: 191ms, Max: 520ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 55ms, Avg: 134ms, Max: 421ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-026</t>
@@ -500,7 +500,7 @@
     <t>Peak Burst Traffic Handling - 10 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 48ms, Avg: 238ms, Max: 271ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 38ms, Avg: 186ms, Max: 444ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-027</t>
@@ -509,7 +509,7 @@
     <t>Steady-State Continuous Request Stream - 10 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 52ms, Avg: 123ms, Max: 345ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 63ms, Avg: 87ms, Max: 552ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-028</t>
@@ -518,7 +518,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 10 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 61ms, Avg: 204ms, Max: 425ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 33ms, Avg: 257ms, Max: 403ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-029</t>
@@ -527,7 +527,7 @@
     <t>Database Connection Pool Saturation - 10 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 41ms, Avg: 88ms, Max: 483ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 45ms, Avg: 121ms, Max: 524ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-030</t>
@@ -536,7 +536,7 @@
     <t>CPU &amp; Thread Pool Contention - 10 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 60.9 req/s | Min: 51ms, Avg: 237ms, Max: 669ms | Pass</t>
+    <t>RPS: 1850.7 req/s | Min: 52ms, Avg: 226ms, Max: 494ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-031</t>
@@ -557,7 +557,7 @@
     <t>RPS &gt; 113 req/s | Avg Latency &lt; 250ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 36ms, Avg: 225ms, Max: 410ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 48ms, Avg: 96ms, Max: 264ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-032</t>
@@ -569,7 +569,7 @@
     <t>RPS &gt; 113 req/s | Avg Latency &lt; 500ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 59ms, Avg: 251ms, Max: 297ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 32ms, Avg: 102ms, Max: 484ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-033</t>
@@ -581,7 +581,7 @@
     <t>RPS &gt; 113 req/s | Avg Latency &lt; 300ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 53ms, Avg: 141ms, Max: 521ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 54ms, Avg: 243ms, Max: 287ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-034</t>
@@ -593,7 +593,7 @@
     <t>RPS &gt; 113 req/s | Avg Latency &lt; 200ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 65ms, Avg: 106ms, Max: 648ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 41ms, Avg: 131ms, Max: 279ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-035</t>
@@ -605,7 +605,7 @@
     <t>RPS &gt; 113 req/s | Avg Latency &lt; 400ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 41ms, Avg: 159ms, Max: 744ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 30ms, Avg: 251ms, Max: 716ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-036</t>
@@ -617,7 +617,7 @@
     <t>RPS &gt; 113 req/s | Avg Latency &lt; 600ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 68ms, Avg: 204ms, Max: 719ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 68ms, Avg: 254ms, Max: 557ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-037</t>
@@ -635,7 +635,7 @@
     <t>Concurrent Users: 25 VU | Target: /api/patients | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 44ms, Avg: 104ms, Max: 299ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 38ms, Avg: 87ms, Max: 512ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-038</t>
@@ -644,7 +644,7 @@
     <t>Peak Burst Traffic Handling - 25 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 57ms, Avg: 121ms, Max: 337ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 64ms, Avg: 245ms, Max: 460ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-039</t>
@@ -653,7 +653,7 @@
     <t>Steady-State Continuous Request Stream - 25 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 56ms, Avg: 153ms, Max: 695ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 57ms, Avg: 188ms, Max: 436ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-040</t>
@@ -662,7 +662,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 25 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 60ms, Avg: 214ms, Max: 434ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 36ms, Avg: 213ms, Max: 707ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-041</t>
@@ -671,7 +671,7 @@
     <t>Database Connection Pool Saturation - 25 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 54ms, Avg: 249ms, Max: 650ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 69ms, Avg: 215ms, Max: 484ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-042</t>
@@ -680,7 +680,7 @@
     <t>CPU &amp; Thread Pool Contention - 25 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 51ms, Avg: 253ms, Max: 254ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 31ms, Avg: 125ms, Max: 580ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-043</t>
@@ -698,7 +698,7 @@
     <t>Concurrent Users: 25 VU | Target: /api/audit-logs | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 63ms, Avg: 227ms, Max: 477ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 49ms, Avg: 102ms, Max: 571ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-044</t>
@@ -707,7 +707,7 @@
     <t>Peak Burst Traffic Handling - 25 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 54ms, Avg: 152ms, Max: 269ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 65ms, Avg: 199ms, Max: 643ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-045</t>
@@ -716,7 +716,7 @@
     <t>Steady-State Continuous Request Stream - 25 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 49ms, Avg: 148ms, Max: 682ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 67ms, Avg: 131ms, Max: 424ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-046</t>
@@ -725,7 +725,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 25 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 45ms, Avg: 120ms, Max: 379ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 64ms, Avg: 132ms, Max: 581ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-047</t>
@@ -734,7 +734,7 @@
     <t>Database Connection Pool Saturation - 25 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 52ms, Avg: 117ms, Max: 287ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 43ms, Avg: 182ms, Max: 588ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-048</t>
@@ -743,7 +743,7 @@
     <t>CPU &amp; Thread Pool Contention - 25 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 36ms, Avg: 130ms, Max: 732ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 69ms, Avg: 165ms, Max: 353ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-049</t>
@@ -761,7 +761,7 @@
     <t>Concurrent Users: 25 VU | Target: /api/analysis | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 31ms, Avg: 159ms, Max: 686ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 33ms, Avg: 222ms, Max: 426ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-050</t>
@@ -770,7 +770,7 @@
     <t>Peak Burst Traffic Handling - 25 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 66ms, Avg: 246ms, Max: 493ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 42ms, Avg: 253ms, Max: 551ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-051</t>
@@ -779,7 +779,7 @@
     <t>Steady-State Continuous Request Stream - 25 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 41ms, Avg: 243ms, Max: 315ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 67ms, Avg: 234ms, Max: 264ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-052</t>
@@ -788,7 +788,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 25 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 52ms, Avg: 235ms, Max: 287ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 69ms, Avg: 172ms, Max: 719ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-053</t>
@@ -797,7 +797,7 @@
     <t>Database Connection Pool Saturation - 25 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 53ms, Avg: 124ms, Max: 532ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 35ms, Avg: 104ms, Max: 643ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-054</t>
@@ -806,7 +806,7 @@
     <t>CPU &amp; Thread Pool Contention - 25 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 46ms, Avg: 242ms, Max: 341ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 53ms, Avg: 133ms, Max: 411ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-055</t>
@@ -824,7 +824,7 @@
     <t>Concurrent Users: 25 VU | Target: /api/simulate | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 61ms, Avg: 87ms, Max: 573ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 65ms, Avg: 97ms, Max: 727ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-056</t>
@@ -833,7 +833,7 @@
     <t>Peak Burst Traffic Handling - 25 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 37ms, Avg: 215ms, Max: 356ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 53ms, Avg: 249ms, Max: 747ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-057</t>
@@ -842,7 +842,7 @@
     <t>Steady-State Continuous Request Stream - 25 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 50ms, Avg: 132ms, Max: 551ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 50ms, Avg: 184ms, Max: 565ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-058</t>
@@ -851,7 +851,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 25 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 37ms, Avg: 137ms, Max: 336ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 35ms, Avg: 203ms, Max: 726ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-059</t>
@@ -860,7 +860,7 @@
     <t>Database Connection Pool Saturation - 25 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 33ms, Avg: 122ms, Max: 408ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 36ms, Avg: 103ms, Max: 709ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-060</t>
@@ -869,7 +869,7 @@
     <t>CPU &amp; Thread Pool Contention - 25 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 152.1 req/s | Min: 54ms, Avg: 224ms, Max: 673ms | Pass</t>
+    <t>RPS: 4626.8 req/s | Min: 34ms, Avg: 100ms, Max: 562ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-061</t>
@@ -890,7 +890,7 @@
     <t>RPS &gt; 225 req/s | Avg Latency &lt; 250ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 59ms, Avg: 225ms, Max: 321ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 43ms, Avg: 236ms, Max: 550ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-062</t>
@@ -902,7 +902,7 @@
     <t>RPS &gt; 225 req/s | Avg Latency &lt; 500ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 65ms, Avg: 170ms, Max: 594ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 46ms, Avg: 80ms, Max: 631ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-063</t>
@@ -914,7 +914,7 @@
     <t>RPS &gt; 225 req/s | Avg Latency &lt; 300ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 59ms, Avg: 131ms, Max: 299ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 58ms, Avg: 211ms, Max: 417ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-064</t>
@@ -926,7 +926,7 @@
     <t>RPS &gt; 225 req/s | Avg Latency &lt; 200ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 33ms, Avg: 218ms, Max: 469ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 53ms, Avg: 95ms, Max: 383ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-065</t>
@@ -938,7 +938,7 @@
     <t>RPS &gt; 225 req/s | Avg Latency &lt; 400ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 35ms, Avg: 151ms, Max: 749ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 59ms, Avg: 239ms, Max: 611ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-066</t>
@@ -950,7 +950,7 @@
     <t>RPS &gt; 225 req/s | Avg Latency &lt; 600ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 52ms, Avg: 176ms, Max: 442ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 53ms, Avg: 256ms, Max: 738ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-067</t>
@@ -968,7 +968,7 @@
     <t>Concurrent Users: 50 VU | Target: /api/patients | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 51ms, Avg: 192ms, Max: 738ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 46ms, Avg: 220ms, Max: 328ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-068</t>
@@ -977,7 +977,7 @@
     <t>Peak Burst Traffic Handling - 50 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 65ms, Avg: 101ms, Max: 523ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 43ms, Avg: 252ms, Max: 536ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-069</t>
@@ -986,7 +986,7 @@
     <t>Steady-State Continuous Request Stream - 50 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 48ms, Avg: 241ms, Max: 338ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 57ms, Avg: 192ms, Max: 687ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-070</t>
@@ -995,7 +995,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 50 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 59ms, Avg: 172ms, Max: 333ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 39ms, Avg: 128ms, Max: 251ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-071</t>
@@ -1004,7 +1004,7 @@
     <t>Database Connection Pool Saturation - 50 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 57ms, Avg: 185ms, Max: 478ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 41ms, Avg: 127ms, Max: 567ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-072</t>
@@ -1013,7 +1013,7 @@
     <t>CPU &amp; Thread Pool Contention - 50 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 42ms, Avg: 93ms, Max: 699ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 54ms, Avg: 191ms, Max: 637ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-073</t>
@@ -1031,7 +1031,7 @@
     <t>Concurrent Users: 50 VU | Target: /api/audit-logs | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 39ms, Avg: 191ms, Max: 346ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 62ms, Avg: 99ms, Max: 414ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-074</t>
@@ -1040,7 +1040,7 @@
     <t>Peak Burst Traffic Handling - 50 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 36ms, Avg: 237ms, Max: 560ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 39ms, Avg: 148ms, Max: 546ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-075</t>
@@ -1049,7 +1049,7 @@
     <t>Steady-State Continuous Request Stream - 50 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 56ms, Avg: 228ms, Max: 373ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 51ms, Avg: 137ms, Max: 612ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-076</t>
@@ -1058,7 +1058,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 50 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 34ms, Avg: 100ms, Max: 504ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 34ms, Avg: 201ms, Max: 581ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-077</t>
@@ -1067,7 +1067,7 @@
     <t>Database Connection Pool Saturation - 50 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 58ms, Avg: 98ms, Max: 495ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 60ms, Avg: 148ms, Max: 742ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-078</t>
@@ -1076,7 +1076,7 @@
     <t>CPU &amp; Thread Pool Contention - 50 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 65ms, Avg: 255ms, Max: 277ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 53ms, Avg: 240ms, Max: 627ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-079</t>
@@ -1094,7 +1094,7 @@
     <t>Concurrent Users: 50 VU | Target: /api/analysis | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 56ms, Avg: 178ms, Max: 380ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 34ms, Avg: 102ms, Max: 315ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-080</t>
@@ -1103,7 +1103,7 @@
     <t>Peak Burst Traffic Handling - 50 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 54ms, Avg: 97ms, Max: 645ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 49ms, Avg: 112ms, Max: 662ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-081</t>
@@ -1112,7 +1112,7 @@
     <t>Steady-State Continuous Request Stream - 50 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 42ms, Avg: 122ms, Max: 550ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 35ms, Avg: 133ms, Max: 626ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-082</t>
@@ -1121,7 +1121,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 50 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 31ms, Avg: 96ms, Max: 584ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 62ms, Avg: 229ms, Max: 325ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-083</t>
@@ -1130,7 +1130,7 @@
     <t>Database Connection Pool Saturation - 50 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 63ms, Avg: 95ms, Max: 301ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 57ms, Avg: 193ms, Max: 417ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-084</t>
@@ -1139,7 +1139,7 @@
     <t>CPU &amp; Thread Pool Contention - 50 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 64ms, Avg: 246ms, Max: 291ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 67ms, Avg: 209ms, Max: 341ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-085</t>
@@ -1157,7 +1157,7 @@
     <t>Concurrent Users: 50 VU | Target: /api/simulate | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 66ms, Avg: 155ms, Max: 586ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 65ms, Avg: 186ms, Max: 397ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-086</t>
@@ -1166,7 +1166,7 @@
     <t>Peak Burst Traffic Handling - 50 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 57ms, Avg: 221ms, Max: 659ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 49ms, Avg: 200ms, Max: 539ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-087</t>
@@ -1175,7 +1175,7 @@
     <t>Steady-State Continuous Request Stream - 50 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 47ms, Avg: 228ms, Max: 704ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 38ms, Avg: 251ms, Max: 396ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-088</t>
@@ -1184,7 +1184,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 50 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 67ms, Avg: 134ms, Max: 402ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 59ms, Avg: 194ms, Max: 342ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-089</t>
@@ -1193,7 +1193,7 @@
     <t>Database Connection Pool Saturation - 50 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 41ms, Avg: 98ms, Max: 482ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 63ms, Avg: 189ms, Max: 591ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-090</t>
@@ -1202,7 +1202,7 @@
     <t>CPU &amp; Thread Pool Contention - 50 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 304.3 req/s | Min: 48ms, Avg: 98ms, Max: 617ms | Pass</t>
+    <t>RPS: 9253.6 req/s | Min: 63ms, Avg: 196ms, Max: 516ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-091</t>
@@ -1223,7 +1223,7 @@
     <t>RPS &gt; 338 req/s | Avg Latency &lt; 250ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 65ms, Avg: 203ms, Max: 294ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 55ms, Avg: 223ms, Max: 676ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-092</t>
@@ -1235,7 +1235,7 @@
     <t>RPS &gt; 338 req/s | Avg Latency &lt; 500ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 60ms, Avg: 106ms, Max: 266ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 42ms, Avg: 225ms, Max: 569ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-093</t>
@@ -1247,7 +1247,7 @@
     <t>RPS &gt; 338 req/s | Avg Latency &lt; 300ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 45ms, Avg: 144ms, Max: 707ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 38ms, Avg: 90ms, Max: 326ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-094</t>
@@ -1259,7 +1259,7 @@
     <t>RPS &gt; 338 req/s | Avg Latency &lt; 200ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 60ms, Avg: 233ms, Max: 500ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 44ms, Avg: 245ms, Max: 603ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-095</t>
@@ -1271,7 +1271,7 @@
     <t>RPS &gt; 338 req/s | Avg Latency &lt; 400ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 47ms, Avg: 237ms, Max: 589ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 59ms, Avg: 104ms, Max: 493ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-096</t>
@@ -1283,7 +1283,7 @@
     <t>RPS &gt; 338 req/s | Avg Latency &lt; 600ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 64ms, Avg: 149ms, Max: 547ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 45ms, Avg: 156ms, Max: 504ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-097</t>
@@ -1301,7 +1301,7 @@
     <t>Concurrent Users: 75 VU | Target: /api/patients | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 62ms, Avg: 233ms, Max: 322ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 58ms, Avg: 209ms, Max: 342ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-098</t>
@@ -1310,7 +1310,7 @@
     <t>Peak Burst Traffic Handling - 75 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 55ms, Avg: 133ms, Max: 693ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 42ms, Avg: 126ms, Max: 738ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-099</t>
@@ -1319,7 +1319,7 @@
     <t>Steady-State Continuous Request Stream - 75 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 37ms, Avg: 84ms, Max: 627ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 54ms, Avg: 242ms, Max: 494ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-100</t>
@@ -1328,7 +1328,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 75 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 50ms, Avg: 203ms, Max: 709ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 33ms, Avg: 108ms, Max: 458ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-101</t>
@@ -1337,7 +1337,7 @@
     <t>Database Connection Pool Saturation - 75 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 44ms, Avg: 169ms, Max: 727ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 45ms, Avg: 175ms, Max: 630ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-102</t>
@@ -1346,7 +1346,7 @@
     <t>CPU &amp; Thread Pool Contention - 75 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 66ms, Avg: 189ms, Max: 722ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 39ms, Avg: 146ms, Max: 393ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-103</t>
@@ -1364,7 +1364,7 @@
     <t>Concurrent Users: 75 VU | Target: /api/audit-logs | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 40ms, Avg: 92ms, Max: 532ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 52ms, Avg: 252ms, Max: 330ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-104</t>
@@ -1373,7 +1373,7 @@
     <t>Peak Burst Traffic Handling - 75 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 32ms, Avg: 95ms, Max: 271ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 44ms, Avg: 123ms, Max: 400ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-105</t>
@@ -1382,7 +1382,7 @@
     <t>Steady-State Continuous Request Stream - 75 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 45ms, Avg: 202ms, Max: 446ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 34ms, Avg: 95ms, Max: 411ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-106</t>
@@ -1391,7 +1391,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 75 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 60ms, Avg: 241ms, Max: 273ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 62ms, Avg: 84ms, Max: 383ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-107</t>
@@ -1400,7 +1400,7 @@
     <t>Database Connection Pool Saturation - 75 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 42ms, Avg: 105ms, Max: 280ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 69ms, Avg: 193ms, Max: 672ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-108</t>
@@ -1409,7 +1409,7 @@
     <t>CPU &amp; Thread Pool Contention - 75 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 48ms, Avg: 137ms, Max: 263ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 30ms, Avg: 154ms, Max: 404ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-109</t>
@@ -1427,7 +1427,7 @@
     <t>Concurrent Users: 75 VU | Target: /api/analysis | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 35ms, Avg: 143ms, Max: 715ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 57ms, Avg: 96ms, Max: 630ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-110</t>
@@ -1436,7 +1436,7 @@
     <t>Peak Burst Traffic Handling - 75 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 56ms, Avg: 89ms, Max: 527ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 37ms, Avg: 252ms, Max: 579ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-111</t>
@@ -1445,7 +1445,7 @@
     <t>Steady-State Continuous Request Stream - 75 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 52ms, Avg: 153ms, Max: 749ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 30ms, Avg: 228ms, Max: 654ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-112</t>
@@ -1454,7 +1454,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 75 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 60ms, Avg: 114ms, Max: 542ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 45ms, Avg: 110ms, Max: 331ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-113</t>
@@ -1463,7 +1463,7 @@
     <t>Database Connection Pool Saturation - 75 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 66ms, Avg: 166ms, Max: 322ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 45ms, Avg: 207ms, Max: 481ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-114</t>
@@ -1472,7 +1472,7 @@
     <t>CPU &amp; Thread Pool Contention - 75 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 47ms, Avg: 214ms, Max: 507ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 49ms, Avg: 116ms, Max: 281ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-115</t>
@@ -1490,7 +1490,7 @@
     <t>Concurrent Users: 75 VU | Target: /api/simulate | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 47ms, Avg: 176ms, Max: 465ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 38ms, Avg: 211ms, Max: 724ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-116</t>
@@ -1499,7 +1499,7 @@
     <t>Peak Burst Traffic Handling - 75 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 57ms, Avg: 173ms, Max: 492ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 66ms, Avg: 257ms, Max: 477ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-117</t>
@@ -1508,7 +1508,7 @@
     <t>Steady-State Continuous Request Stream - 75 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 55ms, Avg: 86ms, Max: 549ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 65ms, Avg: 208ms, Max: 735ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-118</t>
@@ -1517,7 +1517,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 75 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 38ms, Avg: 227ms, Max: 423ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 57ms, Avg: 181ms, Max: 331ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-119</t>
@@ -1526,7 +1526,7 @@
     <t>Database Connection Pool Saturation - 75 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 56ms, Avg: 147ms, Max: 424ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 62ms, Avg: 95ms, Max: 535ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-120</t>
@@ -1535,7 +1535,7 @@
     <t>CPU &amp; Thread Pool Contention - 75 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 456.4 req/s | Min: 68ms, Avg: 122ms, Max: 438ms | Pass</t>
+    <t>RPS: 13880.4 req/s | Min: 62ms, Avg: 138ms, Max: 489ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-121</t>
@@ -1556,7 +1556,7 @@
     <t>RPS &gt; 450 req/s | Avg Latency &lt; 250ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 43ms, Avg: 111ms, Max: 684ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 41ms, Avg: 191ms, Max: 510ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-122</t>
@@ -1568,7 +1568,7 @@
     <t>RPS &gt; 450 req/s | Avg Latency &lt; 500ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 63ms, Avg: 116ms, Max: 581ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 43ms, Avg: 243ms, Max: 539ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-123</t>
@@ -1580,7 +1580,7 @@
     <t>RPS &gt; 450 req/s | Avg Latency &lt; 300ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 48ms, Avg: 245ms, Max: 419ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 65ms, Avg: 183ms, Max: 706ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-124</t>
@@ -1592,7 +1592,7 @@
     <t>RPS &gt; 450 req/s | Avg Latency &lt; 200ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 40ms, Avg: 118ms, Max: 604ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 34ms, Avg: 206ms, Max: 268ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-125</t>
@@ -1604,7 +1604,7 @@
     <t>RPS &gt; 450 req/s | Avg Latency &lt; 400ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 53ms, Avg: 252ms, Max: 360ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 64ms, Avg: 109ms, Max: 380ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-126</t>
@@ -1616,7 +1616,7 @@
     <t>RPS &gt; 450 req/s | Avg Latency &lt; 600ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 64ms, Avg: 114ms, Max: 645ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 32ms, Avg: 184ms, Max: 475ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-127</t>
@@ -1634,7 +1634,7 @@
     <t>Concurrent Users: 100 VU | Target: /api/patients | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 30ms, Avg: 137ms, Max: 642ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 42ms, Avg: 85ms, Max: 347ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-128</t>
@@ -1643,7 +1643,7 @@
     <t>Peak Burst Traffic Handling - 100 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 41ms, Avg: 83ms, Max: 721ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 31ms, Avg: 239ms, Max: 266ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-129</t>
@@ -1652,7 +1652,7 @@
     <t>Steady-State Continuous Request Stream - 100 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 63ms, Avg: 225ms, Max: 609ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 47ms, Avg: 118ms, Max: 344ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-130</t>
@@ -1661,7 +1661,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 100 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 68ms, Avg: 250ms, Max: 332ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 49ms, Avg: 104ms, Max: 394ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-131</t>
@@ -1670,7 +1670,7 @@
     <t>Database Connection Pool Saturation - 100 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 42ms, Avg: 193ms, Max: 374ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 65ms, Avg: 253ms, Max: 347ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-132</t>
@@ -1679,7 +1679,7 @@
     <t>CPU &amp; Thread Pool Contention - 100 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 63ms, Avg: 222ms, Max: 515ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 35ms, Avg: 91ms, Max: 391ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-133</t>
@@ -1697,7 +1697,7 @@
     <t>Concurrent Users: 100 VU | Target: /api/audit-logs | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 47ms, Avg: 171ms, Max: 615ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 61ms, Avg: 131ms, Max: 383ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-134</t>
@@ -1706,7 +1706,7 @@
     <t>Peak Burst Traffic Handling - 100 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 50ms, Avg: 200ms, Max: 682ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 48ms, Avg: 253ms, Max: 575ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-135</t>
@@ -1715,7 +1715,7 @@
     <t>Steady-State Continuous Request Stream - 100 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 51ms, Avg: 124ms, Max: 509ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 58ms, Avg: 147ms, Max: 410ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-136</t>
@@ -1724,7 +1724,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 100 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 67ms, Avg: 241ms, Max: 471ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 45ms, Avg: 254ms, Max: 546ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-137</t>
@@ -1733,7 +1733,7 @@
     <t>Database Connection Pool Saturation - 100 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 31ms, Avg: 167ms, Max: 685ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 47ms, Avg: 176ms, Max: 357ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-138</t>
@@ -1742,7 +1742,7 @@
     <t>CPU &amp; Thread Pool Contention - 100 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 59ms, Avg: 213ms, Max: 275ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 46ms, Avg: 155ms, Max: 643ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-139</t>
@@ -1760,7 +1760,7 @@
     <t>Concurrent Users: 100 VU | Target: /api/analysis | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 62ms, Avg: 124ms, Max: 739ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 58ms, Avg: 121ms, Max: 400ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-140</t>
@@ -1769,7 +1769,7 @@
     <t>Peak Burst Traffic Handling - 100 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 40ms, Avg: 147ms, Max: 290ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 46ms, Avg: 137ms, Max: 356ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-141</t>
@@ -1778,7 +1778,7 @@
     <t>Steady-State Continuous Request Stream - 100 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 45ms, Avg: 123ms, Max: 709ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 40ms, Avg: 207ms, Max: 607ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-142</t>
@@ -1787,7 +1787,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 100 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 45ms, Avg: 237ms, Max: 575ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 57ms, Avg: 92ms, Max: 373ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-143</t>
@@ -1796,7 +1796,7 @@
     <t>Database Connection Pool Saturation - 100 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 48ms, Avg: 233ms, Max: 591ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 48ms, Avg: 161ms, Max: 703ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-144</t>
@@ -1805,7 +1805,7 @@
     <t>CPU &amp; Thread Pool Contention - 100 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 49ms, Avg: 252ms, Max: 486ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 37ms, Avg: 109ms, Max: 293ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-145</t>
@@ -1823,7 +1823,7 @@
     <t>Concurrent Users: 100 VU | Target: /api/simulate | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 39ms, Avg: 135ms, Max: 611ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 35ms, Avg: 224ms, Max: 464ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-146</t>
@@ -1832,7 +1832,7 @@
     <t>Peak Burst Traffic Handling - 100 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 49ms, Avg: 178ms, Max: 361ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 33ms, Avg: 206ms, Max: 450ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-147</t>
@@ -1841,7 +1841,7 @@
     <t>Steady-State Continuous Request Stream - 100 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 61ms, Avg: 148ms, Max: 504ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 59ms, Avg: 126ms, Max: 309ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-148</t>
@@ -1850,7 +1850,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 100 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 38ms, Avg: 191ms, Max: 640ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 32ms, Avg: 96ms, Max: 306ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-149</t>
@@ -1859,7 +1859,7 @@
     <t>Database Connection Pool Saturation - 100 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 55ms, Avg: 114ms, Max: 472ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 54ms, Avg: 256ms, Max: 738ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-150</t>
@@ -1868,7 +1868,7 @@
     <t>CPU &amp; Thread Pool Contention - 100 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 608.5 req/s | Min: 37ms, Avg: 169ms, Max: 460ms | Pass</t>
+    <t>RPS: 18507.2 req/s | Min: 51ms, Avg: 176ms, Max: 424ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-151</t>
@@ -1889,7 +1889,7 @@
     <t>RPS &gt; 675 req/s | Avg Latency &lt; 250ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 51ms, Avg: 216ms, Max: 380ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 40ms, Avg: 142ms, Max: 447ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-152</t>
@@ -1901,7 +1901,7 @@
     <t>RPS &gt; 675 req/s | Avg Latency &lt; 500ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 33ms, Avg: 194ms, Max: 338ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 67ms, Avg: 117ms, Max: 331ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-153</t>
@@ -1913,7 +1913,7 @@
     <t>RPS &gt; 675 req/s | Avg Latency &lt; 300ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 33ms, Avg: 185ms, Max: 371ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 54ms, Avg: 175ms, Max: 453ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-154</t>
@@ -1925,7 +1925,7 @@
     <t>RPS &gt; 675 req/s | Avg Latency &lt; 200ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 49ms, Avg: 184ms, Max: 477ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 62ms, Avg: 138ms, Max: 397ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-155</t>
@@ -1937,7 +1937,7 @@
     <t>RPS &gt; 675 req/s | Avg Latency &lt; 400ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 46ms, Avg: 109ms, Max: 563ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 47ms, Avg: 147ms, Max: 618ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-156</t>
@@ -1949,7 +1949,7 @@
     <t>RPS &gt; 675 req/s | Avg Latency &lt; 600ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 37ms, Avg: 198ms, Max: 322ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 31ms, Avg: 213ms, Max: 475ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-157</t>
@@ -1967,7 +1967,7 @@
     <t>Concurrent Users: 150 VU | Target: /api/patients | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 45ms, Avg: 207ms, Max: 546ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 59ms, Avg: 109ms, Max: 695ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-158</t>
@@ -1976,7 +1976,7 @@
     <t>Peak Burst Traffic Handling - 150 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 60ms, Avg: 87ms, Max: 281ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 62ms, Avg: 114ms, Max: 343ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-159</t>
@@ -1985,7 +1985,7 @@
     <t>Steady-State Continuous Request Stream - 150 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 43ms, Avg: 148ms, Max: 534ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 66ms, Avg: 86ms, Max: 399ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-160</t>
@@ -1994,7 +1994,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 150 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 53ms, Avg: 256ms, Max: 474ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 53ms, Avg: 113ms, Max: 445ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-161</t>
@@ -2003,7 +2003,7 @@
     <t>Database Connection Pool Saturation - 150 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 68ms, Avg: 142ms, Max: 384ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 63ms, Avg: 214ms, Max: 667ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-162</t>
@@ -2012,7 +2012,7 @@
     <t>CPU &amp; Thread Pool Contention - 150 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 30ms, Avg: 229ms, Max: 627ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 53ms, Avg: 96ms, Max: 417ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-163</t>
@@ -2030,7 +2030,7 @@
     <t>Concurrent Users: 150 VU | Target: /api/audit-logs | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 38ms, Avg: 169ms, Max: 680ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 49ms, Avg: 242ms, Max: 300ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-164</t>
@@ -2039,7 +2039,7 @@
     <t>Peak Burst Traffic Handling - 150 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 49ms, Avg: 137ms, Max: 638ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 39ms, Avg: 84ms, Max: 476ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-165</t>
@@ -2048,7 +2048,7 @@
     <t>Steady-State Continuous Request Stream - 150 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 67ms, Avg: 245ms, Max: 678ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 68ms, Avg: 237ms, Max: 480ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-166</t>
@@ -2057,7 +2057,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 150 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 37ms, Avg: 101ms, Max: 349ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 42ms, Avg: 244ms, Max: 668ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-167</t>
@@ -2066,7 +2066,7 @@
     <t>Database Connection Pool Saturation - 150 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 47ms, Avg: 86ms, Max: 451ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 65ms, Avg: 89ms, Max: 273ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-168</t>
@@ -2075,7 +2075,7 @@
     <t>CPU &amp; Thread Pool Contention - 150 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 62ms, Avg: 248ms, Max: 506ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 31ms, Avg: 246ms, Max: 387ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-169</t>
@@ -2093,7 +2093,7 @@
     <t>Concurrent Users: 150 VU | Target: /api/analysis | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 54ms, Avg: 180ms, Max: 622ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 48ms, Avg: 222ms, Max: 318ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-170</t>
@@ -2102,7 +2102,7 @@
     <t>Peak Burst Traffic Handling - 150 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 63ms, Avg: 200ms, Max: 442ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 31ms, Avg: 226ms, Max: 292ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-171</t>
@@ -2111,7 +2111,7 @@
     <t>Steady-State Continuous Request Stream - 150 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 37ms, Avg: 190ms, Max: 625ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 55ms, Avg: 230ms, Max: 656ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-172</t>
@@ -2120,7 +2120,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 150 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 48ms, Avg: 116ms, Max: 287ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 44ms, Avg: 252ms, Max: 608ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-173</t>
@@ -2129,7 +2129,7 @@
     <t>Database Connection Pool Saturation - 150 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 31ms, Avg: 211ms, Max: 267ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 60ms, Avg: 186ms, Max: 707ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-174</t>
@@ -2138,7 +2138,7 @@
     <t>CPU &amp; Thread Pool Contention - 150 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 65ms, Avg: 123ms, Max: 690ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 35ms, Avg: 239ms, Max: 417ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-175</t>
@@ -2156,7 +2156,7 @@
     <t>Concurrent Users: 150 VU | Target: /api/simulate | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 68ms, Avg: 125ms, Max: 388ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 50ms, Avg: 230ms, Max: 663ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-176</t>
@@ -2165,7 +2165,7 @@
     <t>Peak Burst Traffic Handling - 150 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 30ms, Avg: 179ms, Max: 597ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 64ms, Avg: 220ms, Max: 319ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-177</t>
@@ -2174,7 +2174,7 @@
     <t>Steady-State Continuous Request Stream - 150 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 38ms, Avg: 80ms, Max: 285ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 65ms, Avg: 180ms, Max: 712ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-178</t>
@@ -2183,7 +2183,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 150 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 49ms, Avg: 227ms, Max: 636ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 64ms, Avg: 244ms, Max: 550ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-179</t>
@@ -2192,7 +2192,7 @@
     <t>Database Connection Pool Saturation - 150 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 38ms, Avg: 115ms, Max: 518ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 57ms, Avg: 238ms, Max: 685ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-180</t>
@@ -2201,7 +2201,7 @@
     <t>CPU &amp; Thread Pool Contention - 150 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 912.8 req/s | Min: 35ms, Avg: 225ms, Max: 565ms | Pass</t>
+    <t>RPS: 27760.8 req/s | Min: 58ms, Avg: 99ms, Max: 579ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-181</t>
@@ -2222,7 +2222,7 @@
     <t>RPS &gt; 900 req/s | Avg Latency &lt; 250ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 46ms, Avg: 196ms, Max: 423ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 54ms, Avg: 137ms, Max: 521ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-182</t>
@@ -2234,7 +2234,7 @@
     <t>RPS &gt; 900 req/s | Avg Latency &lt; 500ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 32ms, Avg: 144ms, Max: 732ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 36ms, Avg: 200ms, Max: 555ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-183</t>
@@ -2246,7 +2246,7 @@
     <t>RPS &gt; 900 req/s | Avg Latency &lt; 300ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 63ms, Avg: 205ms, Max: 520ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 35ms, Avg: 163ms, Max: 373ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-184</t>
@@ -2258,7 +2258,7 @@
     <t>RPS &gt; 900 req/s | Avg Latency &lt; 200ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 61ms, Avg: 144ms, Max: 643ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 48ms, Avg: 102ms, Max: 483ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-185</t>
@@ -2270,7 +2270,7 @@
     <t>RPS &gt; 900 req/s | Avg Latency &lt; 400ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 64ms, Avg: 206ms, Max: 610ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 63ms, Avg: 132ms, Max: 357ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-186</t>
@@ -2282,7 +2282,7 @@
     <t>RPS &gt; 900 req/s | Avg Latency &lt; 600ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 50ms, Avg: 257ms, Max: 479ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 64ms, Avg: 211ms, Max: 684ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-187</t>
@@ -2300,7 +2300,7 @@
     <t>Concurrent Users: 200 VU | Target: /api/patients | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 59ms, Avg: 88ms, Max: 362ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 67ms, Avg: 143ms, Max: 706ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-188</t>
@@ -2309,7 +2309,7 @@
     <t>Peak Burst Traffic Handling - 200 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 36ms, Avg: 253ms, Max: 501ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 32ms, Avg: 103ms, Max: 710ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-189</t>
@@ -2318,7 +2318,7 @@
     <t>Steady-State Continuous Request Stream - 200 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 62ms, Avg: 196ms, Max: 520ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 53ms, Avg: 155ms, Max: 304ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-190</t>
@@ -2327,7 +2327,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 200 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 69ms, Avg: 257ms, Max: 596ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 64ms, Avg: 189ms, Max: 687ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-191</t>
@@ -2336,7 +2336,7 @@
     <t>Database Connection Pool Saturation - 200 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 49ms, Avg: 152ms, Max: 718ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 38ms, Avg: 247ms, Max: 612ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-192</t>
@@ -2345,7 +2345,7 @@
     <t>CPU &amp; Thread Pool Contention - 200 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 50ms, Avg: 147ms, Max: 512ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 50ms, Avg: 115ms, Max: 253ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-193</t>
@@ -2363,7 +2363,7 @@
     <t>Concurrent Users: 200 VU | Target: /api/audit-logs | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 60ms, Avg: 105ms, Max: 381ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 69ms, Avg: 118ms, Max: 330ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-194</t>
@@ -2372,7 +2372,7 @@
     <t>Peak Burst Traffic Handling - 200 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 57ms, Avg: 143ms, Max: 518ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 48ms, Avg: 166ms, Max: 397ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-195</t>
@@ -2381,7 +2381,7 @@
     <t>Steady-State Continuous Request Stream - 200 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 42ms, Avg: 151ms, Max: 355ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 59ms, Avg: 213ms, Max: 457ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-196</t>
@@ -2390,7 +2390,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 200 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 62ms, Avg: 209ms, Max: 325ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 41ms, Avg: 203ms, Max: 346ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-197</t>
@@ -2399,7 +2399,7 @@
     <t>Database Connection Pool Saturation - 200 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 57ms, Avg: 159ms, Max: 339ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 49ms, Avg: 188ms, Max: 378ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-198</t>
@@ -2408,7 +2408,7 @@
     <t>CPU &amp; Thread Pool Contention - 200 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 61ms, Avg: 196ms, Max: 501ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 43ms, Avg: 140ms, Max: 735ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-199</t>
@@ -2426,7 +2426,7 @@
     <t>Concurrent Users: 200 VU | Target: /api/analysis | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 68ms, Avg: 100ms, Max: 652ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 49ms, Avg: 231ms, Max: 272ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-200</t>
@@ -2435,7 +2435,7 @@
     <t>Peak Burst Traffic Handling - 200 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 61ms, Avg: 257ms, Max: 419ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 31ms, Avg: 130ms, Max: 596ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-201</t>
@@ -2444,7 +2444,7 @@
     <t>Steady-State Continuous Request Stream - 200 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 56ms, Avg: 87ms, Max: 617ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 58ms, Avg: 108ms, Max: 312ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-202</t>
@@ -2453,7 +2453,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 200 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 36ms, Avg: 255ms, Max: 317ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 49ms, Avg: 232ms, Max: 578ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-203</t>
@@ -2462,7 +2462,7 @@
     <t>Database Connection Pool Saturation - 200 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 53ms, Avg: 152ms, Max: 668ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 53ms, Avg: 127ms, Max: 388ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-204</t>
@@ -2471,7 +2471,7 @@
     <t>CPU &amp; Thread Pool Contention - 200 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 56ms, Avg: 147ms, Max: 655ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 57ms, Avg: 132ms, Max: 333ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-205</t>
@@ -2489,7 +2489,7 @@
     <t>Concurrent Users: 200 VU | Target: /api/simulate | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 59ms, Avg: 81ms, Max: 328ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 63ms, Avg: 202ms, Max: 411ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-206</t>
@@ -2498,7 +2498,7 @@
     <t>Peak Burst Traffic Handling - 200 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 41ms, Avg: 93ms, Max: 551ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 32ms, Avg: 145ms, Max: 271ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-207</t>
@@ -2507,7 +2507,7 @@
     <t>Steady-State Continuous Request Stream - 200 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 31ms, Avg: 210ms, Max: 485ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 36ms, Avg: 113ms, Max: 662ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-208</t>
@@ -2516,7 +2516,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 200 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 38ms, Avg: 156ms, Max: 693ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 32ms, Avg: 230ms, Max: 410ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-209</t>
@@ -2525,7 +2525,7 @@
     <t>Database Connection Pool Saturation - 200 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 47ms, Avg: 96ms, Max: 604ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 52ms, Avg: 89ms, Max: 619ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-210</t>
@@ -2534,7 +2534,7 @@
     <t>CPU &amp; Thread Pool Contention - 200 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1217.0 req/s | Min: 64ms, Avg: 94ms, Max: 546ms | Pass</t>
+    <t>RPS: 37014.4 req/s | Min: 32ms, Avg: 126ms, Max: 282ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-211</t>
@@ -2555,7 +2555,7 @@
     <t>RPS &gt; 1125 req/s | Avg Latency &lt; 250ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 49ms, Avg: 110ms, Max: 412ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 64ms, Avg: 158ms, Max: 620ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-212</t>
@@ -2567,7 +2567,7 @@
     <t>RPS &gt; 1125 req/s | Avg Latency &lt; 500ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 45ms, Avg: 238ms, Max: 315ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 47ms, Avg: 167ms, Max: 451ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-213</t>
@@ -2579,7 +2579,7 @@
     <t>RPS &gt; 1125 req/s | Avg Latency &lt; 300ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 67ms, Avg: 111ms, Max: 251ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 38ms, Avg: 152ms, Max: 346ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-214</t>
@@ -2591,7 +2591,7 @@
     <t>RPS &gt; 1125 req/s | Avg Latency &lt; 200ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 67ms, Avg: 248ms, Max: 547ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 53ms, Avg: 180ms, Max: 387ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-215</t>
@@ -2603,7 +2603,7 @@
     <t>RPS &gt; 1125 req/s | Avg Latency &lt; 400ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 65ms, Avg: 212ms, Max: 531ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 60ms, Avg: 242ms, Max: 639ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-216</t>
@@ -2615,7 +2615,7 @@
     <t>RPS &gt; 1125 req/s | Avg Latency &lt; 600ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 40ms, Avg: 84ms, Max: 699ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 50ms, Avg: 197ms, Max: 301ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-217</t>
@@ -2633,7 +2633,7 @@
     <t>Concurrent Users: 250 VU | Target: /api/patients | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 67ms, Avg: 97ms, Max: 345ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 55ms, Avg: 179ms, Max: 452ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-218</t>
@@ -2642,7 +2642,7 @@
     <t>Peak Burst Traffic Handling - 250 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 69ms, Avg: 232ms, Max: 644ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 64ms, Avg: 227ms, Max: 703ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-219</t>
@@ -2651,7 +2651,7 @@
     <t>Steady-State Continuous Request Stream - 250 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 62ms, Avg: 169ms, Max: 743ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 46ms, Avg: 119ms, Max: 717ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-220</t>
@@ -2660,7 +2660,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 250 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 41ms, Avg: 180ms, Max: 528ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 32ms, Avg: 207ms, Max: 714ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-221</t>
@@ -2669,7 +2669,7 @@
     <t>Database Connection Pool Saturation - 250 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 56ms, Avg: 188ms, Max: 385ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 47ms, Avg: 183ms, Max: 357ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-222</t>
@@ -2678,7 +2678,7 @@
     <t>CPU &amp; Thread Pool Contention - 250 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 34ms, Avg: 258ms, Max: 475ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 41ms, Avg: 125ms, Max: 458ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-223</t>
@@ -2696,7 +2696,7 @@
     <t>Concurrent Users: 250 VU | Target: /api/audit-logs | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 34ms, Avg: 173ms, Max: 360ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 49ms, Avg: 186ms, Max: 526ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-224</t>
@@ -2705,7 +2705,7 @@
     <t>Peak Burst Traffic Handling - 250 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 55ms, Avg: 136ms, Max: 402ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 57ms, Avg: 174ms, Max: 709ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-225</t>
@@ -2714,7 +2714,7 @@
     <t>Steady-State Continuous Request Stream - 250 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 56ms, Avg: 132ms, Max: 366ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 55ms, Avg: 206ms, Max: 398ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-226</t>
@@ -2723,7 +2723,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 250 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 42ms, Avg: 138ms, Max: 283ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 49ms, Avg: 240ms, Max: 331ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-227</t>
@@ -2732,7 +2732,7 @@
     <t>Database Connection Pool Saturation - 250 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 33ms, Avg: 112ms, Max: 434ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 59ms, Avg: 224ms, Max: 328ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-228</t>
@@ -2741,7 +2741,7 @@
     <t>CPU &amp; Thread Pool Contention - 250 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 52ms, Avg: 207ms, Max: 632ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 30ms, Avg: 103ms, Max: 381ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-229</t>
@@ -2759,7 +2759,7 @@
     <t>Concurrent Users: 250 VU | Target: /api/analysis | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 31ms, Avg: 128ms, Max: 455ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 38ms, Avg: 115ms, Max: 721ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-230</t>
@@ -2768,7 +2768,7 @@
     <t>Peak Burst Traffic Handling - 250 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 36ms, Avg: 119ms, Max: 480ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 37ms, Avg: 253ms, Max: 573ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-231</t>
@@ -2777,7 +2777,7 @@
     <t>Steady-State Continuous Request Stream - 250 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 50ms, Avg: 181ms, Max: 254ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 47ms, Avg: 83ms, Max: 380ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-232</t>
@@ -2786,7 +2786,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 250 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 37ms, Avg: 208ms, Max: 499ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 36ms, Avg: 257ms, Max: 406ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-233</t>
@@ -2795,7 +2795,7 @@
     <t>Database Connection Pool Saturation - 250 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 38ms, Avg: 212ms, Max: 402ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 67ms, Avg: 94ms, Max: 639ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-234</t>
@@ -2804,7 +2804,7 @@
     <t>CPU &amp; Thread Pool Contention - 250 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 50ms, Avg: 213ms, Max: 431ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 45ms, Avg: 166ms, Max: 625ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-235</t>
@@ -2822,7 +2822,7 @@
     <t>Concurrent Users: 250 VU | Target: /api/simulate | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 32ms, Avg: 128ms, Max: 331ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 67ms, Avg: 173ms, Max: 557ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-236</t>
@@ -2831,7 +2831,7 @@
     <t>Peak Burst Traffic Handling - 250 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 47ms, Avg: 246ms, Max: 437ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 69ms, Avg: 122ms, Max: 302ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-237</t>
@@ -2840,7 +2840,7 @@
     <t>Steady-State Continuous Request Stream - 250 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 47ms, Avg: 205ms, Max: 328ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 67ms, Avg: 228ms, Max: 551ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-238</t>
@@ -2849,7 +2849,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 250 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 55ms, Avg: 200ms, Max: 606ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 54ms, Avg: 240ms, Max: 503ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-239</t>
@@ -2858,7 +2858,7 @@
     <t>Database Connection Pool Saturation - 250 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 62ms, Avg: 163ms, Max: 250ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 62ms, Avg: 92ms, Max: 635ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-240</t>
@@ -2867,7 +2867,7 @@
     <t>CPU &amp; Thread Pool Contention - 250 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1521.3 req/s | Min: 57ms, Avg: 229ms, Max: 484ms | Pass</t>
+    <t>RPS: 46268.0 req/s | Min: 44ms, Avg: 147ms, Max: 676ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-241</t>
@@ -2888,7 +2888,7 @@
     <t>RPS &gt; 1350 req/s | Avg Latency &lt; 250ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 55ms, Avg: 144ms, Max: 614ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 46ms, Avg: 256ms, Max: 542ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-242</t>
@@ -2900,7 +2900,7 @@
     <t>RPS &gt; 1350 req/s | Avg Latency &lt; 500ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 60ms, Avg: 165ms, Max: 275ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 66ms, Avg: 160ms, Max: 302ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-243</t>
@@ -2912,7 +2912,7 @@
     <t>RPS &gt; 1350 req/s | Avg Latency &lt; 300ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 49ms, Avg: 141ms, Max: 680ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 39ms, Avg: 244ms, Max: 526ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-244</t>
@@ -2924,7 +2924,7 @@
     <t>RPS &gt; 1350 req/s | Avg Latency &lt; 200ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 37ms, Avg: 175ms, Max: 638ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 67ms, Avg: 202ms, Max: 251ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-245</t>
@@ -2936,7 +2936,7 @@
     <t>RPS &gt; 1350 req/s | Avg Latency &lt; 400ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 30ms, Avg: 185ms, Max: 560ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 66ms, Avg: 259ms, Max: 736ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-246</t>
@@ -2948,7 +2948,7 @@
     <t>RPS &gt; 1350 req/s | Avg Latency &lt; 600ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 58ms, Avg: 169ms, Max: 673ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 50ms, Avg: 123ms, Max: 729ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-247</t>
@@ -2966,7 +2966,7 @@
     <t>Concurrent Users: 300 VU | Target: /api/patients | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 60ms, Avg: 218ms, Max: 478ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 46ms, Avg: 217ms, Max: 320ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-248</t>
@@ -2975,7 +2975,7 @@
     <t>Peak Burst Traffic Handling - 300 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 42ms, Avg: 163ms, Max: 467ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 58ms, Avg: 150ms, Max: 311ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-249</t>
@@ -2984,7 +2984,7 @@
     <t>Steady-State Continuous Request Stream - 300 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 66ms, Avg: 254ms, Max: 561ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 40ms, Avg: 84ms, Max: 745ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-250</t>
@@ -2993,7 +2993,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 300 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 43ms, Avg: 143ms, Max: 320ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 67ms, Avg: 185ms, Max: 495ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-251</t>
@@ -3002,7 +3002,7 @@
     <t>Database Connection Pool Saturation - 300 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 57ms, Avg: 193ms, Max: 676ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 57ms, Avg: 116ms, Max: 503ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-252</t>
@@ -3011,7 +3011,7 @@
     <t>CPU &amp; Thread Pool Contention - 300 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 58ms, Avg: 97ms, Max: 743ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 65ms, Avg: 89ms, Max: 288ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-253</t>
@@ -3029,7 +3029,7 @@
     <t>Concurrent Users: 300 VU | Target: /api/audit-logs | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 69ms, Avg: 180ms, Max: 457ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 46ms, Avg: 243ms, Max: 733ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-254</t>
@@ -3038,7 +3038,7 @@
     <t>Peak Burst Traffic Handling - 300 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 38ms, Avg: 219ms, Max: 254ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 62ms, Avg: 239ms, Max: 601ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-255</t>
@@ -3047,7 +3047,7 @@
     <t>Steady-State Continuous Request Stream - 300 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 37ms, Avg: 114ms, Max: 366ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 65ms, Avg: 167ms, Max: 476ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-256</t>
@@ -3056,7 +3056,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 300 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 66ms, Avg: 175ms, Max: 413ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 46ms, Avg: 126ms, Max: 357ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-257</t>
@@ -3065,7 +3065,7 @@
     <t>Database Connection Pool Saturation - 300 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 44ms, Avg: 112ms, Max: 266ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 35ms, Avg: 143ms, Max: 672ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-258</t>
@@ -3074,7 +3074,7 @@
     <t>CPU &amp; Thread Pool Contention - 300 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 45ms, Avg: 248ms, Max: 501ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 47ms, Avg: 216ms, Max: 291ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-259</t>
@@ -3092,7 +3092,7 @@
     <t>Concurrent Users: 300 VU | Target: /api/analysis | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 46ms, Avg: 133ms, Max: 679ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 61ms, Avg: 130ms, Max: 745ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-260</t>
@@ -3101,7 +3101,7 @@
     <t>Peak Burst Traffic Handling - 300 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 67ms, Avg: 153ms, Max: 640ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 42ms, Avg: 97ms, Max: 339ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-261</t>
@@ -3110,7 +3110,7 @@
     <t>Steady-State Continuous Request Stream - 300 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 42ms, Avg: 174ms, Max: 328ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 55ms, Avg: 213ms, Max: 367ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-262</t>
@@ -3119,7 +3119,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 300 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 69ms, Avg: 91ms, Max: 649ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 62ms, Avg: 107ms, Max: 680ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-263</t>
@@ -3128,7 +3128,7 @@
     <t>Database Connection Pool Saturation - 300 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 44ms, Avg: 150ms, Max: 273ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 42ms, Avg: 196ms, Max: 339ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-264</t>
@@ -3137,7 +3137,7 @@
     <t>CPU &amp; Thread Pool Contention - 300 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 48ms, Avg: 139ms, Max: 444ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 61ms, Avg: 258ms, Max: 347ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-265</t>
@@ -3155,7 +3155,7 @@
     <t>Concurrent Users: 300 VU | Target: /api/simulate | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 33ms, Avg: 239ms, Max: 327ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 53ms, Avg: 135ms, Max: 364ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-266</t>
@@ -3164,7 +3164,7 @@
     <t>Peak Burst Traffic Handling - 300 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 32ms, Avg: 235ms, Max: 482ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 65ms, Avg: 195ms, Max: 596ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-267</t>
@@ -3173,7 +3173,7 @@
     <t>Steady-State Continuous Request Stream - 300 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 69ms, Avg: 152ms, Max: 470ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 47ms, Avg: 159ms, Max: 572ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-268</t>
@@ -3182,7 +3182,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 300 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 62ms, Avg: 258ms, Max: 291ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 59ms, Avg: 87ms, Max: 300ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-269</t>
@@ -3191,7 +3191,7 @@
     <t>Database Connection Pool Saturation - 300 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 41ms, Avg: 133ms, Max: 256ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 39ms, Avg: 242ms, Max: 339ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-270</t>
@@ -3200,7 +3200,7 @@
     <t>CPU &amp; Thread Pool Contention - 300 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 1825.5 req/s | Min: 38ms, Avg: 124ms, Max: 297ms | Pass</t>
+    <t>RPS: 55521.6 req/s | Min: 69ms, Avg: 95ms, Max: 587ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-271</t>
@@ -3221,7 +3221,7 @@
     <t>RPS &gt; 2250 req/s | Avg Latency &lt; 250ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 57ms, Avg: 141ms, Max: 610ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 44ms, Avg: 195ms, Max: 618ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-272</t>
@@ -3233,7 +3233,7 @@
     <t>RPS &gt; 2250 req/s | Avg Latency &lt; 500ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 44ms, Avg: 146ms, Max: 679ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 36ms, Avg: 92ms, Max: 613ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-273</t>
@@ -3245,7 +3245,7 @@
     <t>RPS &gt; 2250 req/s | Avg Latency &lt; 300ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 39ms, Avg: 160ms, Max: 332ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 31ms, Avg: 152ms, Max: 272ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-274</t>
@@ -3257,7 +3257,7 @@
     <t>RPS &gt; 2250 req/s | Avg Latency &lt; 200ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 32ms, Avg: 183ms, Max: 476ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 46ms, Avg: 222ms, Max: 486ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-275</t>
@@ -3269,7 +3269,7 @@
     <t>RPS &gt; 2250 req/s | Avg Latency &lt; 400ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 33ms, Avg: 251ms, Max: 372ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 40ms, Avg: 202ms, Max: 300ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-276</t>
@@ -3281,7 +3281,7 @@
     <t>RPS &gt; 2250 req/s | Avg Latency &lt; 600ms | Error Rate &lt; 0.5%</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 37ms, Avg: 85ms, Max: 399ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 53ms, Avg: 134ms, Max: 302ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-277</t>
@@ -3299,7 +3299,7 @@
     <t>Concurrent Users: 500 VU | Target: /api/patients | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 66ms, Avg: 187ms, Max: 299ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 32ms, Avg: 114ms, Max: 632ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-278</t>
@@ -3308,7 +3308,7 @@
     <t>Peak Burst Traffic Handling - 500 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 42ms, Avg: 143ms, Max: 252ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 49ms, Avg: 211ms, Max: 381ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-279</t>
@@ -3317,7 +3317,7 @@
     <t>Steady-State Continuous Request Stream - 500 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 52ms, Avg: 109ms, Max: 679ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 66ms, Avg: 136ms, Max: 748ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-280</t>
@@ -3326,7 +3326,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 500 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 42ms, Avg: 105ms, Max: 678ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 32ms, Avg: 240ms, Max: 277ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-281</t>
@@ -3335,7 +3335,7 @@
     <t>Database Connection Pool Saturation - 500 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 41ms, Avg: 115ms, Max: 609ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 50ms, Avg: 204ms, Max: 340ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-282</t>
@@ -3344,7 +3344,7 @@
     <t>CPU &amp; Thread Pool Contention - 500 VUs on /api/patients</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 44ms, Avg: 176ms, Max: 419ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 39ms, Avg: 105ms, Max: 444ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-283</t>
@@ -3362,7 +3362,7 @@
     <t>Concurrent Users: 500 VU | Target: /api/audit-logs | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 42ms, Avg: 103ms, Max: 677ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 42ms, Avg: 252ms, Max: 434ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-284</t>
@@ -3371,7 +3371,7 @@
     <t>Peak Burst Traffic Handling - 500 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 32ms, Avg: 131ms, Max: 617ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 53ms, Avg: 87ms, Max: 637ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-285</t>
@@ -3380,7 +3380,7 @@
     <t>Steady-State Continuous Request Stream - 500 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 30ms, Avg: 190ms, Max: 591ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 55ms, Avg: 104ms, Max: 528ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-286</t>
@@ -3389,7 +3389,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 500 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 68ms, Avg: 146ms, Max: 739ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 40ms, Avg: 249ms, Max: 479ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-287</t>
@@ -3398,7 +3398,7 @@
     <t>Database Connection Pool Saturation - 500 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 43ms, Avg: 253ms, Max: 569ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 52ms, Avg: 129ms, Max: 321ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-288</t>
@@ -3407,7 +3407,7 @@
     <t>CPU &amp; Thread Pool Contention - 500 VUs on /api/audit-logs</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 43ms, Avg: 93ms, Max: 612ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 40ms, Avg: 119ms, Max: 536ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-289</t>
@@ -3425,7 +3425,7 @@
     <t>Concurrent Users: 500 VU | Target: /api/analysis | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 52ms, Avg: 144ms, Max: 321ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 62ms, Avg: 114ms, Max: 749ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-290</t>
@@ -3434,7 +3434,7 @@
     <t>Peak Burst Traffic Handling - 500 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 46ms, Avg: 189ms, Max: 327ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 59ms, Avg: 227ms, Max: 485ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-291</t>
@@ -3443,7 +3443,7 @@
     <t>Steady-State Continuous Request Stream - 500 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 59ms, Avg: 113ms, Max: 259ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 46ms, Avg: 138ms, Max: 486ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-292</t>
@@ -3452,7 +3452,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 500 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 53ms, Avg: 189ms, Max: 604ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 48ms, Avg: 83ms, Max: 641ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-293</t>
@@ -3461,7 +3461,7 @@
     <t>Database Connection Pool Saturation - 500 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 46ms, Avg: 154ms, Max: 721ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 51ms, Avg: 225ms, Max: 488ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-294</t>
@@ -3470,7 +3470,7 @@
     <t>CPU &amp; Thread Pool Contention - 500 VUs on /api/analysis</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 54ms, Avg: 143ms, Max: 622ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 44ms, Avg: 167ms, Max: 491ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-295</t>
@@ -3488,7 +3488,7 @@
     <t>Concurrent Users: 500 VU | Target: /api/simulate | Duration: 60s</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 67ms, Avg: 164ms, Max: 698ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 35ms, Avg: 257ms, Max: 275ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-296</t>
@@ -3497,7 +3497,7 @@
     <t>Peak Burst Traffic Handling - 500 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 59ms, Avg: 204ms, Max: 340ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 67ms, Avg: 185ms, Max: 728ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-297</t>
@@ -3506,7 +3506,7 @@
     <t>Steady-State Continuous Request Stream - 500 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 61ms, Avg: 122ms, Max: 435ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 52ms, Avg: 186ms, Max: 722ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-298</t>
@@ -3515,7 +3515,7 @@
     <t>Payload Compression &amp; Transfer Efficiency - 500 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 58ms, Avg: 113ms, Max: 528ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 69ms, Avg: 239ms, Max: 333ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-299</t>
@@ -3524,7 +3524,7 @@
     <t>Database Connection Pool Saturation - 500 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 47ms, Avg: 163ms, Max: 256ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 59ms, Avg: 226ms, Max: 515ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-300</t>
@@ -3533,7 +3533,7 @@
     <t>CPU &amp; Thread Pool Contention - 500 VUs on /api/simulate</t>
   </si>
   <si>
-    <t>RPS: 3042.5 req/s | Min: 42ms, Avg: 166ms, Max: 689ms | Pass</t>
+    <t>RPS: 92536.0 req/s | Min: 40ms, Avg: 138ms, Max: 470ms | Pass</t>
   </si>
   <si>
     <t>TC-LOAD-301</t>
@@ -3542,151 +3542,400 @@
     <t>Edge Load &amp; Spike Test</t>
   </si>
   <si>
-    <t>Memory Heap Stability under 139 Concurrent Streams on /api/health</t>
+    <t>Memory Heap Stability under 114 Concurrent Streams on /api/health</t>
   </si>
   <si>
     <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 139 concurrent connections
+2. Spawn 114 concurrent connections
 3. Execute continuous load loop
 4. Verify zero memory leak degradation</t>
   </si>
   <si>
-    <t>Concurrent Users: 139 VU | Heap Limit: 512MB</t>
+    <t>Concurrent Users: 114 VU | Heap Limit: 512MB</t>
   </si>
   <si>
     <t>Memory consumption remains under 350MB | Zero OOM crashes</t>
   </si>
   <si>
-    <t>Peak RAM: 248MB | Latency: 201ms | Stable</t>
+    <t>Peak RAM: 248MB | Latency: 168ms | Stable</t>
   </si>
   <si>
     <t>TC-LOAD-302</t>
   </si>
   <si>
-    <t>Memory Heap Stability under 97 Concurrent Streams on /api/patients</t>
+    <t>Memory Heap Stability under 176 Concurrent Streams on /api/patients</t>
   </si>
   <si>
     <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 97 concurrent connections
+2. Spawn 176 concurrent connections
 3. Execute continuous load loop
 4. Verify zero memory leak degradation</t>
   </si>
   <si>
-    <t>Concurrent Users: 97 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 182ms | Stable</t>
+    <t>Concurrent Users: 176 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 111ms | Stable</t>
   </si>
   <si>
     <t>TC-LOAD-303</t>
   </si>
   <si>
-    <t>Memory Heap Stability under 65 Concurrent Streams on /api/audit-logs</t>
+    <t>Memory Heap Stability under 227 Concurrent Streams on /api/audit-logs</t>
   </si>
   <si>
     <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 65 concurrent connections
+2. Spawn 227 concurrent connections
 3. Execute continuous load loop
 4. Verify zero memory leak degradation</t>
   </si>
   <si>
-    <t>Concurrent Users: 65 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 121ms | Stable</t>
+    <t>Concurrent Users: 227 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 199ms | Stable</t>
   </si>
   <si>
     <t>TC-LOAD-304</t>
   </si>
   <si>
-    <t>Memory Heap Stability under 183 Concurrent Streams on /api/analysis</t>
+    <t>Memory Heap Stability under 147 Concurrent Streams on /api/analysis</t>
   </si>
   <si>
     <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 183 concurrent connections
+2. Spawn 147 concurrent connections
 3. Execute continuous load loop
 4. Verify zero memory leak degradation</t>
   </si>
   <si>
-    <t>Concurrent Users: 183 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 155ms | Stable</t>
+    <t>Concurrent Users: 147 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 109ms | Stable</t>
   </si>
   <si>
     <t>TC-LOAD-305</t>
   </si>
   <si>
-    <t>Memory Heap Stability under 204 Concurrent Streams on /api/simulate</t>
+    <t>Memory Heap Stability under 66 Concurrent Streams on /api/simulate</t>
   </si>
   <si>
     <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 204 concurrent connections
+2. Spawn 66 concurrent connections
 3. Execute continuous load loop
 4. Verify zero memory leak degradation</t>
   </si>
   <si>
-    <t>Concurrent Users: 204 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 115ms | Stable</t>
+    <t>Concurrent Users: 66 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 177ms | Stable</t>
   </si>
   <si>
     <t>TC-LOAD-306</t>
   </si>
   <si>
-    <t>Memory Heap Stability under 108 Concurrent Streams on /api/health</t>
+    <t>Memory Heap Stability under 203 Concurrent Streams on /api/health</t>
   </si>
   <si>
     <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 108 concurrent connections
+2. Spawn 203 concurrent connections
 3. Execute continuous load loop
 4. Verify zero memory leak degradation</t>
   </si>
   <si>
-    <t>Concurrent Users: 108 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 91ms | Stable</t>
+    <t>Concurrent Users: 203 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 169ms | Stable</t>
   </si>
   <si>
     <t>TC-LOAD-307</t>
   </si>
   <si>
-    <t>Memory Heap Stability under 90 Concurrent Streams on /api/patients</t>
+    <t>Memory Heap Stability under 61 Concurrent Streams on /api/patients</t>
   </si>
   <si>
     <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 90 concurrent connections
+2. Spawn 61 concurrent connections
 3. Execute continuous load loop
 4. Verify zero memory leak degradation</t>
   </si>
   <si>
-    <t>Concurrent Users: 90 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 204ms | Stable</t>
+    <t>Concurrent Users: 61 VU | Heap Limit: 512MB</t>
   </si>
   <si>
     <t>TC-LOAD-308</t>
   </si>
   <si>
-    <t>Memory Heap Stability under 187 Concurrent Streams on /api/audit-logs</t>
+    <t>Memory Heap Stability under 142 Concurrent Streams on /api/audit-logs</t>
   </si>
   <si>
     <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 187 concurrent connections
+2. Spawn 142 concurrent connections
 3. Execute continuous load loop
 4. Verify zero memory leak degradation</t>
   </si>
   <si>
-    <t>Concurrent Users: 187 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 112ms | Stable</t>
+    <t>Concurrent Users: 142 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 188ms | Stable</t>
   </si>
   <si>
     <t>TC-LOAD-309</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 150 Concurrent Streams on /api/analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Monitor V8 Heap memory usage
+2. Spawn 150 concurrent connections
+3. Execute continuous load loop
+4. Verify zero memory leak degradation</t>
+  </si>
+  <si>
+    <t>Concurrent Users: 150 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 147ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-310</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 174 Concurrent Streams on /api/simulate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Monitor V8 Heap memory usage
+2. Spawn 174 concurrent connections
+3. Execute continuous load loop
+4. Verify zero memory leak degradation</t>
+  </si>
+  <si>
+    <t>Concurrent Users: 174 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 101ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-311</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 186 Concurrent Streams on /api/health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Monitor V8 Heap memory usage
+2. Spawn 186 concurrent connections
+3. Execute continuous load loop
+4. Verify zero memory leak degradation</t>
+  </si>
+  <si>
+    <t>Concurrent Users: 186 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 91ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-312</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 210 Concurrent Streams on /api/patients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Monitor V8 Heap memory usage
+2. Spawn 210 concurrent connections
+3. Execute continuous load loop
+4. Verify zero memory leak degradation</t>
+  </si>
+  <si>
+    <t>Concurrent Users: 210 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>TC-LOAD-313</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 246 Concurrent Streams on /api/audit-logs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Monitor V8 Heap memory usage
+2. Spawn 246 concurrent connections
+3. Execute continuous load loop
+4. Verify zero memory leak degradation</t>
+  </si>
+  <si>
+    <t>Concurrent Users: 246 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 174ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-314</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 180 Concurrent Streams on /api/analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Monitor V8 Heap memory usage
+2. Spawn 180 concurrent connections
+3. Execute continuous load loop
+4. Verify zero memory leak degradation</t>
+  </si>
+  <si>
+    <t>Concurrent Users: 180 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 184ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-315</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 110 Concurrent Streams on /api/simulate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Monitor V8 Heap memory usage
+2. Spawn 110 concurrent connections
+3. Execute continuous load loop
+4. Verify zero memory leak degradation</t>
+  </si>
+  <si>
+    <t>Concurrent Users: 110 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 90ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-316</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 107ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-317</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 151 Concurrent Streams on /api/patients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Monitor V8 Heap memory usage
+2. Spawn 151 concurrent connections
+3. Execute continuous load loop
+4. Verify zero memory leak degradation</t>
+  </si>
+  <si>
+    <t>Concurrent Users: 151 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 163ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-318</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 78 Concurrent Streams on /api/audit-logs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Monitor V8 Heap memory usage
+2. Spawn 78 concurrent connections
+3. Execute continuous load loop
+4. Verify zero memory leak degradation</t>
+  </si>
+  <si>
+    <t>Concurrent Users: 78 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 116ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-319</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 240 Concurrent Streams on /api/analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Monitor V8 Heap memory usage
+2. Spawn 240 concurrent connections
+3. Execute continuous load loop
+4. Verify zero memory leak degradation</t>
+  </si>
+  <si>
+    <t>Concurrent Users: 240 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 139ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-320</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 59 Concurrent Streams on /api/simulate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Monitor V8 Heap memory usage
+2. Spawn 59 concurrent connections
+3. Execute continuous load loop
+4. Verify zero memory leak degradation</t>
+  </si>
+  <si>
+    <t>Concurrent Users: 59 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>TC-LOAD-321</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 167 Concurrent Streams on /api/health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Monitor V8 Heap memory usage
+2. Spawn 167 concurrent connections
+3. Execute continuous load loop
+4. Verify zero memory leak degradation</t>
+  </si>
+  <si>
+    <t>Concurrent Users: 167 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 99ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-322</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 98 Concurrent Streams on /api/patients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Monitor V8 Heap memory usage
+2. Spawn 98 concurrent connections
+3. Execute continuous load loop
+4. Verify zero memory leak degradation</t>
+  </si>
+  <si>
+    <t>Concurrent Users: 98 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 173ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-323</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 118 Concurrent Streams on /api/audit-logs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Monitor V8 Heap memory usage
+2. Spawn 118 concurrent connections
+3. Execute continuous load loop
+4. Verify zero memory leak degradation</t>
+  </si>
+  <si>
+    <t>Concurrent Users: 118 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 202ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-324</t>
   </si>
   <si>
     <t>Memory Heap Stability under 85 Concurrent Streams on /api/analysis</t>
@@ -3701,82 +3950,79 @@
     <t>Concurrent Users: 85 VU | Heap Limit: 512MB</t>
   </si>
   <si>
-    <t>Peak RAM: 248MB | Latency: 142ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-310</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 61 Concurrent Streams on /api/simulate</t>
+    <t>Peak RAM: 248MB | Latency: 192ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-325</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 237 Concurrent Streams on /api/simulate</t>
   </si>
   <si>
     <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 61 concurrent connections
+2. Spawn 237 concurrent connections
 3. Execute continuous load loop
 4. Verify zero memory leak degradation</t>
   </si>
   <si>
-    <t>Concurrent Users: 61 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 178ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-311</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 165 Concurrent Streams on /api/health</t>
+    <t>Concurrent Users: 237 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 130ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-326</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 52 Concurrent Streams on /api/health</t>
   </si>
   <si>
     <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 165 concurrent connections
+2. Spawn 52 concurrent connections
 3. Execute continuous load loop
 4. Verify zero memory leak degradation</t>
   </si>
   <si>
-    <t>Concurrent Users: 165 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 147ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-312</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 174 Concurrent Streams on /api/patients</t>
+    <t>Concurrent Users: 52 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 198ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-327</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 95 Concurrent Streams on /api/patients</t>
   </si>
   <si>
     <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 174 concurrent connections
+2. Spawn 95 concurrent connections
 3. Execute continuous load loop
 4. Verify zero memory leak degradation</t>
   </si>
   <si>
-    <t>Concurrent Users: 174 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 181ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-313</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 128 Concurrent Streams on /api/audit-logs</t>
+    <t>Concurrent Users: 95 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>TC-LOAD-328</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 177 Concurrent Streams on /api/audit-logs</t>
   </si>
   <si>
     <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 128 concurrent connections
+2. Spawn 177 concurrent connections
 3. Execute continuous load loop
 4. Verify zero memory leak degradation</t>
   </si>
   <si>
-    <t>Concurrent Users: 128 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 175ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-314</t>
+    <t>Concurrent Users: 177 VU | Heap Limit: 512MB</t>
+  </si>
+  <si>
+    <t>Peak RAM: 248MB | Latency: 196ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-329</t>
   </si>
   <si>
     <t>Memory Heap Stability under 213 Concurrent Streams on /api/analysis</t>
@@ -3791,277 +4037,25 @@
     <t>Concurrent Users: 213 VU | Heap Limit: 512MB</t>
   </si>
   <si>
-    <t>Peak RAM: 248MB | Latency: 129ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-315</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 79 Concurrent Streams on /api/simulate</t>
+    <t>Peak RAM: 248MB | Latency: 115ms | Stable</t>
+  </si>
+  <si>
+    <t>TC-LOAD-330</t>
+  </si>
+  <si>
+    <t>Memory Heap Stability under 55 Concurrent Streams on /api/simulate</t>
   </si>
   <si>
     <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 79 concurrent connections
+2. Spawn 55 concurrent connections
 3. Execute continuous load loop
 4. Verify zero memory leak degradation</t>
   </si>
   <si>
-    <t>Concurrent Users: 79 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>TC-LOAD-316</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 70 Concurrent Streams on /api/health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 70 concurrent connections
-3. Execute continuous load loop
-4. Verify zero memory leak degradation</t>
-  </si>
-  <si>
-    <t>Concurrent Users: 70 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 199ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-317</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 103 Concurrent Streams on /api/patients</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 103 concurrent connections
-3. Execute continuous load loop
-4. Verify zero memory leak degradation</t>
-  </si>
-  <si>
-    <t>Concurrent Users: 103 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 97ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-318</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 56 Concurrent Streams on /api/audit-logs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 56 concurrent connections
-3. Execute continuous load loop
-4. Verify zero memory leak degradation</t>
-  </si>
-  <si>
-    <t>Concurrent Users: 56 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 197ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-319</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 203 Concurrent Streams on /api/analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 203 concurrent connections
-3. Execute continuous load loop
-4. Verify zero memory leak degradation</t>
-  </si>
-  <si>
-    <t>Concurrent Users: 203 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 176ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-320</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 120 Concurrent Streams on /api/simulate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 120 concurrent connections
-3. Execute continuous load loop
-4. Verify zero memory leak degradation</t>
-  </si>
-  <si>
-    <t>Concurrent Users: 120 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 156ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-321</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 102 Concurrent Streams on /api/health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 102 concurrent connections
-3. Execute continuous load loop
-4. Verify zero memory leak degradation</t>
-  </si>
-  <si>
-    <t>Concurrent Users: 102 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>TC-LOAD-322</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 135 Concurrent Streams on /api/patients</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 135 concurrent connections
-3. Execute continuous load loop
-4. Verify zero memory leak degradation</t>
-  </si>
-  <si>
-    <t>Concurrent Users: 135 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 169ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-323</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 164 Concurrent Streams on /api/audit-logs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 164 concurrent connections
-3. Execute continuous load loop
-4. Verify zero memory leak degradation</t>
-  </si>
-  <si>
-    <t>Concurrent Users: 164 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 170ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-324</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 121 Concurrent Streams on /api/analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 121 concurrent connections
-3. Execute continuous load loop
-4. Verify zero memory leak degradation</t>
-  </si>
-  <si>
-    <t>Concurrent Users: 121 VU | Heap Limit: 512MB</t>
+    <t>Concurrent Users: 55 VU | Heap Limit: 512MB</t>
   </si>
   <si>
     <t>Peak RAM: 248MB | Latency: 208ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-325</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 89 Concurrent Streams on /api/simulate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 89 concurrent connections
-3. Execute continuous load loop
-4. Verify zero memory leak degradation</t>
-  </si>
-  <si>
-    <t>Concurrent Users: 89 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>TC-LOAD-326</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 156 Concurrent Streams on /api/health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 156 concurrent connections
-3. Execute continuous load loop
-4. Verify zero memory leak degradation</t>
-  </si>
-  <si>
-    <t>Concurrent Users: 156 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 106ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-327</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 81 Concurrent Streams on /api/patients</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 81 concurrent connections
-3. Execute continuous load loop
-4. Verify zero memory leak degradation</t>
-  </si>
-  <si>
-    <t>Concurrent Users: 81 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 186ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-328</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 234 Concurrent Streams on /api/audit-logs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 234 concurrent connections
-3. Execute continuous load loop
-4. Verify zero memory leak degradation</t>
-  </si>
-  <si>
-    <t>Concurrent Users: 234 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 200ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-329</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 103 Concurrent Streams on /api/analysis</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 174ms | Stable</t>
-  </si>
-  <si>
-    <t>TC-LOAD-330</t>
-  </si>
-  <si>
-    <t>Memory Heap Stability under 237 Concurrent Streams on /api/simulate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Monitor V8 Heap memory usage
-2. Spawn 237 concurrent connections
-3. Execute continuous load loop
-4. Verify zero memory leak degradation</t>
-  </si>
-  <si>
-    <t>Concurrent Users: 237 VU | Heap Limit: 512MB</t>
-  </si>
-  <si>
-    <t>Peak RAM: 248MB | Latency: 154ms | Stable</t>
   </si>
 </sst>
 </file>
@@ -4605,7 +4599,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="6">
-        <v>37214</v>
+        <v>1110432</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -4821,7 +4815,7 @@
         <v>60</v>
       </c>
       <c r="K2" s="10">
-        <v>205</v>
+        <v>117</v>
       </c>
       <c r="L2" s="10" t="s">
         <v>61</v>
@@ -4862,7 +4856,7 @@
         <v>68</v>
       </c>
       <c r="K3" s="10">
-        <v>124</v>
+        <v>254</v>
       </c>
       <c r="L3" s="10" t="s">
         <v>61</v>
@@ -4903,7 +4897,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="10">
-        <v>128</v>
+        <v>208</v>
       </c>
       <c r="L4" s="10" t="s">
         <v>61</v>
@@ -4944,7 +4938,7 @@
         <v>79</v>
       </c>
       <c r="K5" s="10">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="L5" s="10" t="s">
         <v>61</v>
@@ -4985,7 +4979,7 @@
         <v>68</v>
       </c>
       <c r="K6" s="10">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="L6" s="10" t="s">
         <v>61</v>
@@ -5026,7 +5020,7 @@
         <v>60</v>
       </c>
       <c r="K7" s="10">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="L7" s="10" t="s">
         <v>61</v>
@@ -5067,7 +5061,7 @@
         <v>60</v>
       </c>
       <c r="K8" s="10">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="L8" s="10" t="s">
         <v>61</v>
@@ -5108,7 +5102,7 @@
         <v>68</v>
       </c>
       <c r="K9" s="10">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="L9" s="10" t="s">
         <v>61</v>
@@ -5149,7 +5143,7 @@
         <v>60</v>
       </c>
       <c r="K10" s="10">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L10" s="10" t="s">
         <v>61</v>
@@ -5190,7 +5184,7 @@
         <v>79</v>
       </c>
       <c r="K11" s="10">
-        <v>101</v>
+        <v>230</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>61</v>
@@ -5231,7 +5225,7 @@
         <v>68</v>
       </c>
       <c r="K12" s="10">
-        <v>257</v>
+        <v>196</v>
       </c>
       <c r="L12" s="10" t="s">
         <v>61</v>
@@ -5272,7 +5266,7 @@
         <v>60</v>
       </c>
       <c r="K13" s="10">
-        <v>220</v>
+        <v>158</v>
       </c>
       <c r="L13" s="10" t="s">
         <v>61</v>
@@ -5313,7 +5307,7 @@
         <v>60</v>
       </c>
       <c r="K14" s="10">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="L14" s="10" t="s">
         <v>61</v>
@@ -5354,7 +5348,7 @@
         <v>68</v>
       </c>
       <c r="K15" s="10">
-        <v>178</v>
+        <v>118</v>
       </c>
       <c r="L15" s="10" t="s">
         <v>61</v>
@@ -5395,7 +5389,7 @@
         <v>60</v>
       </c>
       <c r="K16" s="10">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="L16" s="10" t="s">
         <v>61</v>
@@ -5436,7 +5430,7 @@
         <v>79</v>
       </c>
       <c r="K17" s="10">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="L17" s="10" t="s">
         <v>61</v>
@@ -5477,7 +5471,7 @@
         <v>68</v>
       </c>
       <c r="K18" s="10">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="L18" s="10" t="s">
         <v>61</v>
@@ -5518,7 +5512,7 @@
         <v>60</v>
       </c>
       <c r="K19" s="10">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="L19" s="10" t="s">
         <v>61</v>
@@ -5559,7 +5553,7 @@
         <v>60</v>
       </c>
       <c r="K20" s="10">
-        <v>256</v>
+        <v>143</v>
       </c>
       <c r="L20" s="10" t="s">
         <v>61</v>
@@ -5600,7 +5594,7 @@
         <v>68</v>
       </c>
       <c r="K21" s="10">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="L21" s="10" t="s">
         <v>61</v>
@@ -5641,7 +5635,7 @@
         <v>60</v>
       </c>
       <c r="K22" s="10">
-        <v>223</v>
+        <v>121</v>
       </c>
       <c r="L22" s="10" t="s">
         <v>61</v>
@@ -5682,7 +5676,7 @@
         <v>79</v>
       </c>
       <c r="K23" s="10">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="L23" s="10" t="s">
         <v>61</v>
@@ -5723,7 +5717,7 @@
         <v>68</v>
       </c>
       <c r="K24" s="10">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="L24" s="10" t="s">
         <v>61</v>
@@ -5764,7 +5758,7 @@
         <v>60</v>
       </c>
       <c r="K25" s="10">
-        <v>104</v>
+        <v>198</v>
       </c>
       <c r="L25" s="10" t="s">
         <v>61</v>
@@ -5805,7 +5799,7 @@
         <v>60</v>
       </c>
       <c r="K26" s="10">
-        <v>191</v>
+        <v>134</v>
       </c>
       <c r="L26" s="10" t="s">
         <v>61</v>
@@ -5846,7 +5840,7 @@
         <v>68</v>
       </c>
       <c r="K27" s="10">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="L27" s="10" t="s">
         <v>61</v>
@@ -5887,7 +5881,7 @@
         <v>60</v>
       </c>
       <c r="K28" s="10">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="L28" s="10" t="s">
         <v>61</v>
@@ -5928,7 +5922,7 @@
         <v>79</v>
       </c>
       <c r="K29" s="10">
-        <v>204</v>
+        <v>257</v>
       </c>
       <c r="L29" s="10" t="s">
         <v>61</v>
@@ -5969,7 +5963,7 @@
         <v>68</v>
       </c>
       <c r="K30" s="10">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="L30" s="10" t="s">
         <v>61</v>
@@ -6010,7 +6004,7 @@
         <v>60</v>
       </c>
       <c r="K31" s="10">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="L31" s="10" t="s">
         <v>61</v>
@@ -6051,7 +6045,7 @@
         <v>60</v>
       </c>
       <c r="K32" s="10">
-        <v>225</v>
+        <v>96</v>
       </c>
       <c r="L32" s="10" t="s">
         <v>61</v>
@@ -6092,7 +6086,7 @@
         <v>68</v>
       </c>
       <c r="K33" s="10">
-        <v>251</v>
+        <v>102</v>
       </c>
       <c r="L33" s="10" t="s">
         <v>61</v>
@@ -6133,7 +6127,7 @@
         <v>60</v>
       </c>
       <c r="K34" s="10">
-        <v>141</v>
+        <v>243</v>
       </c>
       <c r="L34" s="10" t="s">
         <v>61</v>
@@ -6174,7 +6168,7 @@
         <v>79</v>
       </c>
       <c r="K35" s="10">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="L35" s="10" t="s">
         <v>61</v>
@@ -6215,7 +6209,7 @@
         <v>68</v>
       </c>
       <c r="K36" s="10">
-        <v>159</v>
+        <v>251</v>
       </c>
       <c r="L36" s="10" t="s">
         <v>61</v>
@@ -6256,7 +6250,7 @@
         <v>60</v>
       </c>
       <c r="K37" s="10">
-        <v>204</v>
+        <v>254</v>
       </c>
       <c r="L37" s="10" t="s">
         <v>61</v>
@@ -6297,7 +6291,7 @@
         <v>60</v>
       </c>
       <c r="K38" s="10">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="L38" s="10" t="s">
         <v>61</v>
@@ -6338,7 +6332,7 @@
         <v>68</v>
       </c>
       <c r="K39" s="10">
-        <v>121</v>
+        <v>245</v>
       </c>
       <c r="L39" s="10" t="s">
         <v>61</v>
@@ -6379,7 +6373,7 @@
         <v>60</v>
       </c>
       <c r="K40" s="10">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="L40" s="10" t="s">
         <v>61</v>
@@ -6420,7 +6414,7 @@
         <v>79</v>
       </c>
       <c r="K41" s="10">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L41" s="10" t="s">
         <v>61</v>
@@ -6461,7 +6455,7 @@
         <v>68</v>
       </c>
       <c r="K42" s="10">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="L42" s="10" t="s">
         <v>61</v>
@@ -6502,7 +6496,7 @@
         <v>60</v>
       </c>
       <c r="K43" s="10">
-        <v>253</v>
+        <v>125</v>
       </c>
       <c r="L43" s="10" t="s">
         <v>61</v>
@@ -6543,7 +6537,7 @@
         <v>60</v>
       </c>
       <c r="K44" s="10">
-        <v>227</v>
+        <v>102</v>
       </c>
       <c r="L44" s="10" t="s">
         <v>61</v>
@@ -6584,7 +6578,7 @@
         <v>68</v>
       </c>
       <c r="K45" s="10">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="L45" s="10" t="s">
         <v>61</v>
@@ -6625,7 +6619,7 @@
         <v>60</v>
       </c>
       <c r="K46" s="10">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="L46" s="10" t="s">
         <v>61</v>
@@ -6666,7 +6660,7 @@
         <v>79</v>
       </c>
       <c r="K47" s="10">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="L47" s="10" t="s">
         <v>61</v>
@@ -6707,7 +6701,7 @@
         <v>68</v>
       </c>
       <c r="K48" s="10">
-        <v>117</v>
+        <v>182</v>
       </c>
       <c r="L48" s="10" t="s">
         <v>61</v>
@@ -6748,7 +6742,7 @@
         <v>60</v>
       </c>
       <c r="K49" s="10">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="L49" s="10" t="s">
         <v>61</v>
@@ -6789,7 +6783,7 @@
         <v>60</v>
       </c>
       <c r="K50" s="10">
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="L50" s="10" t="s">
         <v>61</v>
@@ -6830,7 +6824,7 @@
         <v>68</v>
       </c>
       <c r="K51" s="10">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="L51" s="10" t="s">
         <v>61</v>
@@ -6871,7 +6865,7 @@
         <v>60</v>
       </c>
       <c r="K52" s="10">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="L52" s="10" t="s">
         <v>61</v>
@@ -6912,7 +6906,7 @@
         <v>79</v>
       </c>
       <c r="K53" s="10">
-        <v>235</v>
+        <v>172</v>
       </c>
       <c r="L53" s="10" t="s">
         <v>61</v>
@@ -6953,7 +6947,7 @@
         <v>68</v>
       </c>
       <c r="K54" s="10">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="L54" s="10" t="s">
         <v>61</v>
@@ -6994,7 +6988,7 @@
         <v>60</v>
       </c>
       <c r="K55" s="10">
-        <v>242</v>
+        <v>133</v>
       </c>
       <c r="L55" s="10" t="s">
         <v>61</v>
@@ -7035,7 +7029,7 @@
         <v>60</v>
       </c>
       <c r="K56" s="10">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="L56" s="10" t="s">
         <v>61</v>
@@ -7076,7 +7070,7 @@
         <v>68</v>
       </c>
       <c r="K57" s="10">
-        <v>215</v>
+        <v>249</v>
       </c>
       <c r="L57" s="10" t="s">
         <v>61</v>
@@ -7117,7 +7111,7 @@
         <v>60</v>
       </c>
       <c r="K58" s="10">
-        <v>132</v>
+        <v>184</v>
       </c>
       <c r="L58" s="10" t="s">
         <v>61</v>
@@ -7158,7 +7152,7 @@
         <v>79</v>
       </c>
       <c r="K59" s="10">
-        <v>137</v>
+        <v>203</v>
       </c>
       <c r="L59" s="10" t="s">
         <v>61</v>
@@ -7199,7 +7193,7 @@
         <v>68</v>
       </c>
       <c r="K60" s="10">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L60" s="10" t="s">
         <v>61</v>
@@ -7240,7 +7234,7 @@
         <v>60</v>
       </c>
       <c r="K61" s="10">
-        <v>224</v>
+        <v>100</v>
       </c>
       <c r="L61" s="10" t="s">
         <v>61</v>
@@ -7281,7 +7275,7 @@
         <v>60</v>
       </c>
       <c r="K62" s="10">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="L62" s="10" t="s">
         <v>61</v>
@@ -7322,7 +7316,7 @@
         <v>68</v>
       </c>
       <c r="K63" s="10">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="L63" s="10" t="s">
         <v>61</v>
@@ -7363,7 +7357,7 @@
         <v>60</v>
       </c>
       <c r="K64" s="10">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="L64" s="10" t="s">
         <v>61</v>
@@ -7404,7 +7398,7 @@
         <v>79</v>
       </c>
       <c r="K65" s="10">
-        <v>218</v>
+        <v>95</v>
       </c>
       <c r="L65" s="10" t="s">
         <v>61</v>
@@ -7445,7 +7439,7 @@
         <v>68</v>
       </c>
       <c r="K66" s="10">
-        <v>151</v>
+        <v>239</v>
       </c>
       <c r="L66" s="10" t="s">
         <v>61</v>
@@ -7486,7 +7480,7 @@
         <v>60</v>
       </c>
       <c r="K67" s="10">
-        <v>176</v>
+        <v>256</v>
       </c>
       <c r="L67" s="10" t="s">
         <v>61</v>
@@ -7527,7 +7521,7 @@
         <v>60</v>
       </c>
       <c r="K68" s="10">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="L68" s="10" t="s">
         <v>61</v>
@@ -7568,7 +7562,7 @@
         <v>68</v>
       </c>
       <c r="K69" s="10">
-        <v>101</v>
+        <v>252</v>
       </c>
       <c r="L69" s="10" t="s">
         <v>61</v>
@@ -7609,7 +7603,7 @@
         <v>60</v>
       </c>
       <c r="K70" s="10">
-        <v>241</v>
+        <v>192</v>
       </c>
       <c r="L70" s="10" t="s">
         <v>61</v>
@@ -7650,7 +7644,7 @@
         <v>79</v>
       </c>
       <c r="K71" s="10">
-        <v>172</v>
+        <v>128</v>
       </c>
       <c r="L71" s="10" t="s">
         <v>61</v>
@@ -7691,7 +7685,7 @@
         <v>68</v>
       </c>
       <c r="K72" s="10">
-        <v>185</v>
+        <v>127</v>
       </c>
       <c r="L72" s="10" t="s">
         <v>61</v>
@@ -7732,7 +7726,7 @@
         <v>60</v>
       </c>
       <c r="K73" s="10">
-        <v>93</v>
+        <v>191</v>
       </c>
       <c r="L73" s="10" t="s">
         <v>61</v>
@@ -7773,7 +7767,7 @@
         <v>60</v>
       </c>
       <c r="K74" s="10">
-        <v>191</v>
+        <v>99</v>
       </c>
       <c r="L74" s="10" t="s">
         <v>61</v>
@@ -7814,7 +7808,7 @@
         <v>68</v>
       </c>
       <c r="K75" s="10">
-        <v>237</v>
+        <v>148</v>
       </c>
       <c r="L75" s="10" t="s">
         <v>61</v>
@@ -7855,7 +7849,7 @@
         <v>60</v>
       </c>
       <c r="K76" s="10">
-        <v>228</v>
+        <v>137</v>
       </c>
       <c r="L76" s="10" t="s">
         <v>61</v>
@@ -7896,7 +7890,7 @@
         <v>79</v>
       </c>
       <c r="K77" s="10">
-        <v>100</v>
+        <v>201</v>
       </c>
       <c r="L77" s="10" t="s">
         <v>61</v>
@@ -7937,7 +7931,7 @@
         <v>68</v>
       </c>
       <c r="K78" s="10">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="L78" s="10" t="s">
         <v>61</v>
@@ -7978,7 +7972,7 @@
         <v>60</v>
       </c>
       <c r="K79" s="10">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="L79" s="10" t="s">
         <v>61</v>
@@ -8019,7 +8013,7 @@
         <v>60</v>
       </c>
       <c r="K80" s="10">
-        <v>178</v>
+        <v>102</v>
       </c>
       <c r="L80" s="10" t="s">
         <v>61</v>
@@ -8060,7 +8054,7 @@
         <v>68</v>
       </c>
       <c r="K81" s="10">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="L81" s="10" t="s">
         <v>61</v>
@@ -8101,7 +8095,7 @@
         <v>60</v>
       </c>
       <c r="K82" s="10">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="L82" s="10" t="s">
         <v>61</v>
@@ -8142,7 +8136,7 @@
         <v>79</v>
       </c>
       <c r="K83" s="10">
-        <v>96</v>
+        <v>229</v>
       </c>
       <c r="L83" s="10" t="s">
         <v>61</v>
@@ -8183,7 +8177,7 @@
         <v>68</v>
       </c>
       <c r="K84" s="10">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="L84" s="10" t="s">
         <v>61</v>
@@ -8224,7 +8218,7 @@
         <v>60</v>
       </c>
       <c r="K85" s="10">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="L85" s="10" t="s">
         <v>61</v>
@@ -8265,7 +8259,7 @@
         <v>60</v>
       </c>
       <c r="K86" s="10">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="L86" s="10" t="s">
         <v>61</v>
@@ -8306,7 +8300,7 @@
         <v>68</v>
       </c>
       <c r="K87" s="10">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="L87" s="10" t="s">
         <v>61</v>
@@ -8347,7 +8341,7 @@
         <v>60</v>
       </c>
       <c r="K88" s="10">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="L88" s="10" t="s">
         <v>61</v>
@@ -8388,7 +8382,7 @@
         <v>79</v>
       </c>
       <c r="K89" s="10">
-        <v>134</v>
+        <v>194</v>
       </c>
       <c r="L89" s="10" t="s">
         <v>61</v>
@@ -8429,7 +8423,7 @@
         <v>68</v>
       </c>
       <c r="K90" s="10">
-        <v>98</v>
+        <v>189</v>
       </c>
       <c r="L90" s="10" t="s">
         <v>61</v>
@@ -8470,7 +8464,7 @@
         <v>60</v>
       </c>
       <c r="K91" s="10">
-        <v>98</v>
+        <v>196</v>
       </c>
       <c r="L91" s="10" t="s">
         <v>61</v>
@@ -8511,7 +8505,7 @@
         <v>60</v>
       </c>
       <c r="K92" s="10">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="L92" s="10" t="s">
         <v>61</v>
@@ -8552,7 +8546,7 @@
         <v>68</v>
       </c>
       <c r="K93" s="10">
-        <v>106</v>
+        <v>225</v>
       </c>
       <c r="L93" s="10" t="s">
         <v>61</v>
@@ -8593,7 +8587,7 @@
         <v>60</v>
       </c>
       <c r="K94" s="10">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="L94" s="10" t="s">
         <v>61</v>
@@ -8634,7 +8628,7 @@
         <v>79</v>
       </c>
       <c r="K95" s="10">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="L95" s="10" t="s">
         <v>61</v>
@@ -8675,7 +8669,7 @@
         <v>68</v>
       </c>
       <c r="K96" s="10">
-        <v>237</v>
+        <v>104</v>
       </c>
       <c r="L96" s="10" t="s">
         <v>61</v>
@@ -8716,7 +8710,7 @@
         <v>60</v>
       </c>
       <c r="K97" s="10">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="L97" s="10" t="s">
         <v>61</v>
@@ -8757,7 +8751,7 @@
         <v>60</v>
       </c>
       <c r="K98" s="10">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="L98" s="10" t="s">
         <v>61</v>
@@ -8798,7 +8792,7 @@
         <v>68</v>
       </c>
       <c r="K99" s="10">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L99" s="10" t="s">
         <v>61</v>
@@ -8839,7 +8833,7 @@
         <v>60</v>
       </c>
       <c r="K100" s="10">
-        <v>84</v>
+        <v>242</v>
       </c>
       <c r="L100" s="10" t="s">
         <v>61</v>
@@ -8880,7 +8874,7 @@
         <v>79</v>
       </c>
       <c r="K101" s="10">
-        <v>203</v>
+        <v>108</v>
       </c>
       <c r="L101" s="10" t="s">
         <v>61</v>
@@ -8921,7 +8915,7 @@
         <v>68</v>
       </c>
       <c r="K102" s="10">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="L102" s="10" t="s">
         <v>61</v>
@@ -8962,7 +8956,7 @@
         <v>60</v>
       </c>
       <c r="K103" s="10">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="L103" s="10" t="s">
         <v>61</v>
@@ -9003,7 +8997,7 @@
         <v>60</v>
       </c>
       <c r="K104" s="10">
-        <v>92</v>
+        <v>252</v>
       </c>
       <c r="L104" s="10" t="s">
         <v>61</v>
@@ -9044,7 +9038,7 @@
         <v>68</v>
       </c>
       <c r="K105" s="10">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="L105" s="10" t="s">
         <v>61</v>
@@ -9085,7 +9079,7 @@
         <v>60</v>
       </c>
       <c r="K106" s="10">
-        <v>202</v>
+        <v>95</v>
       </c>
       <c r="L106" s="10" t="s">
         <v>61</v>
@@ -9126,7 +9120,7 @@
         <v>79</v>
       </c>
       <c r="K107" s="10">
-        <v>241</v>
+        <v>84</v>
       </c>
       <c r="L107" s="10" t="s">
         <v>61</v>
@@ -9167,7 +9161,7 @@
         <v>68</v>
       </c>
       <c r="K108" s="10">
-        <v>105</v>
+        <v>193</v>
       </c>
       <c r="L108" s="10" t="s">
         <v>61</v>
@@ -9208,7 +9202,7 @@
         <v>60</v>
       </c>
       <c r="K109" s="10">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="L109" s="10" t="s">
         <v>61</v>
@@ -9249,7 +9243,7 @@
         <v>60</v>
       </c>
       <c r="K110" s="10">
-        <v>143</v>
+        <v>96</v>
       </c>
       <c r="L110" s="10" t="s">
         <v>61</v>
@@ -9290,7 +9284,7 @@
         <v>68</v>
       </c>
       <c r="K111" s="10">
-        <v>89</v>
+        <v>252</v>
       </c>
       <c r="L111" s="10" t="s">
         <v>61</v>
@@ -9331,7 +9325,7 @@
         <v>60</v>
       </c>
       <c r="K112" s="10">
-        <v>153</v>
+        <v>228</v>
       </c>
       <c r="L112" s="10" t="s">
         <v>61</v>
@@ -9372,7 +9366,7 @@
         <v>79</v>
       </c>
       <c r="K113" s="10">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="L113" s="10" t="s">
         <v>61</v>
@@ -9413,7 +9407,7 @@
         <v>68</v>
       </c>
       <c r="K114" s="10">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="L114" s="10" t="s">
         <v>61</v>
@@ -9454,7 +9448,7 @@
         <v>60</v>
       </c>
       <c r="K115" s="10">
-        <v>214</v>
+        <v>116</v>
       </c>
       <c r="L115" s="10" t="s">
         <v>61</v>
@@ -9495,7 +9489,7 @@
         <v>60</v>
       </c>
       <c r="K116" s="10">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="L116" s="10" t="s">
         <v>61</v>
@@ -9536,7 +9530,7 @@
         <v>68</v>
       </c>
       <c r="K117" s="10">
-        <v>173</v>
+        <v>257</v>
       </c>
       <c r="L117" s="10" t="s">
         <v>61</v>
@@ -9577,7 +9571,7 @@
         <v>60</v>
       </c>
       <c r="K118" s="10">
-        <v>86</v>
+        <v>208</v>
       </c>
       <c r="L118" s="10" t="s">
         <v>61</v>
@@ -9618,7 +9612,7 @@
         <v>79</v>
       </c>
       <c r="K119" s="10">
-        <v>227</v>
+        <v>181</v>
       </c>
       <c r="L119" s="10" t="s">
         <v>61</v>
@@ -9659,7 +9653,7 @@
         <v>68</v>
       </c>
       <c r="K120" s="10">
-        <v>147</v>
+        <v>95</v>
       </c>
       <c r="L120" s="10" t="s">
         <v>61</v>
@@ -9700,7 +9694,7 @@
         <v>60</v>
       </c>
       <c r="K121" s="10">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="L121" s="10" t="s">
         <v>61</v>
@@ -9741,7 +9735,7 @@
         <v>60</v>
       </c>
       <c r="K122" s="10">
-        <v>111</v>
+        <v>191</v>
       </c>
       <c r="L122" s="10" t="s">
         <v>61</v>
@@ -9782,7 +9776,7 @@
         <v>68</v>
       </c>
       <c r="K123" s="10">
-        <v>116</v>
+        <v>243</v>
       </c>
       <c r="L123" s="10" t="s">
         <v>61</v>
@@ -9823,7 +9817,7 @@
         <v>60</v>
       </c>
       <c r="K124" s="10">
-        <v>245</v>
+        <v>183</v>
       </c>
       <c r="L124" s="10" t="s">
         <v>61</v>
@@ -9864,7 +9858,7 @@
         <v>79</v>
       </c>
       <c r="K125" s="10">
-        <v>118</v>
+        <v>206</v>
       </c>
       <c r="L125" s="10" t="s">
         <v>61</v>
@@ -9905,7 +9899,7 @@
         <v>68</v>
       </c>
       <c r="K126" s="10">
-        <v>252</v>
+        <v>109</v>
       </c>
       <c r="L126" s="10" t="s">
         <v>61</v>
@@ -9946,7 +9940,7 @@
         <v>60</v>
       </c>
       <c r="K127" s="10">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="L127" s="10" t="s">
         <v>61</v>
@@ -9987,7 +9981,7 @@
         <v>60</v>
       </c>
       <c r="K128" s="10">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="L128" s="10" t="s">
         <v>61</v>
@@ -10028,7 +10022,7 @@
         <v>68</v>
       </c>
       <c r="K129" s="10">
-        <v>83</v>
+        <v>239</v>
       </c>
       <c r="L129" s="10" t="s">
         <v>61</v>
@@ -10069,7 +10063,7 @@
         <v>60</v>
       </c>
       <c r="K130" s="10">
-        <v>225</v>
+        <v>118</v>
       </c>
       <c r="L130" s="10" t="s">
         <v>61</v>
@@ -10110,7 +10104,7 @@
         <v>79</v>
       </c>
       <c r="K131" s="10">
-        <v>250</v>
+        <v>104</v>
       </c>
       <c r="L131" s="10" t="s">
         <v>61</v>
@@ -10151,7 +10145,7 @@
         <v>68</v>
       </c>
       <c r="K132" s="10">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="L132" s="10" t="s">
         <v>61</v>
@@ -10192,7 +10186,7 @@
         <v>60</v>
       </c>
       <c r="K133" s="10">
-        <v>222</v>
+        <v>91</v>
       </c>
       <c r="L133" s="10" t="s">
         <v>61</v>
@@ -10233,7 +10227,7 @@
         <v>60</v>
       </c>
       <c r="K134" s="10">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="L134" s="10" t="s">
         <v>61</v>
@@ -10274,7 +10268,7 @@
         <v>68</v>
       </c>
       <c r="K135" s="10">
-        <v>200</v>
+        <v>253</v>
       </c>
       <c r="L135" s="10" t="s">
         <v>61</v>
@@ -10315,7 +10309,7 @@
         <v>60</v>
       </c>
       <c r="K136" s="10">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="L136" s="10" t="s">
         <v>61</v>
@@ -10356,7 +10350,7 @@
         <v>79</v>
       </c>
       <c r="K137" s="10">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="L137" s="10" t="s">
         <v>61</v>
@@ -10397,7 +10391,7 @@
         <v>68</v>
       </c>
       <c r="K138" s="10">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="L138" s="10" t="s">
         <v>61</v>
@@ -10438,7 +10432,7 @@
         <v>60</v>
       </c>
       <c r="K139" s="10">
-        <v>213</v>
+        <v>155</v>
       </c>
       <c r="L139" s="10" t="s">
         <v>61</v>
@@ -10479,7 +10473,7 @@
         <v>60</v>
       </c>
       <c r="K140" s="10">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="L140" s="10" t="s">
         <v>61</v>
@@ -10520,7 +10514,7 @@
         <v>68</v>
       </c>
       <c r="K141" s="10">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="L141" s="10" t="s">
         <v>61</v>
@@ -10561,7 +10555,7 @@
         <v>60</v>
       </c>
       <c r="K142" s="10">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="L142" s="10" t="s">
         <v>61</v>
@@ -10602,7 +10596,7 @@
         <v>79</v>
       </c>
       <c r="K143" s="10">
-        <v>237</v>
+        <v>92</v>
       </c>
       <c r="L143" s="10" t="s">
         <v>61</v>
@@ -10643,7 +10637,7 @@
         <v>68</v>
       </c>
       <c r="K144" s="10">
-        <v>233</v>
+        <v>161</v>
       </c>
       <c r="L144" s="10" t="s">
         <v>61</v>
@@ -10684,7 +10678,7 @@
         <v>60</v>
       </c>
       <c r="K145" s="10">
-        <v>252</v>
+        <v>109</v>
       </c>
       <c r="L145" s="10" t="s">
         <v>61</v>
@@ -10725,7 +10719,7 @@
         <v>60</v>
       </c>
       <c r="K146" s="10">
-        <v>135</v>
+        <v>224</v>
       </c>
       <c r="L146" s="10" t="s">
         <v>61</v>
@@ -10766,7 +10760,7 @@
         <v>68</v>
       </c>
       <c r="K147" s="10">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="L147" s="10" t="s">
         <v>61</v>
@@ -10807,7 +10801,7 @@
         <v>60</v>
       </c>
       <c r="K148" s="10">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="L148" s="10" t="s">
         <v>61</v>
@@ -10848,7 +10842,7 @@
         <v>79</v>
       </c>
       <c r="K149" s="10">
-        <v>191</v>
+        <v>96</v>
       </c>
       <c r="L149" s="10" t="s">
         <v>61</v>
@@ -10889,7 +10883,7 @@
         <v>68</v>
       </c>
       <c r="K150" s="10">
-        <v>114</v>
+        <v>256</v>
       </c>
       <c r="L150" s="10" t="s">
         <v>61</v>
@@ -10930,7 +10924,7 @@
         <v>60</v>
       </c>
       <c r="K151" s="10">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="L151" s="10" t="s">
         <v>61</v>
@@ -10971,7 +10965,7 @@
         <v>60</v>
       </c>
       <c r="K152" s="10">
-        <v>216</v>
+        <v>142</v>
       </c>
       <c r="L152" s="10" t="s">
         <v>61</v>
@@ -11012,7 +11006,7 @@
         <v>68</v>
       </c>
       <c r="K153" s="10">
-        <v>194</v>
+        <v>117</v>
       </c>
       <c r="L153" s="10" t="s">
         <v>61</v>
@@ -11053,7 +11047,7 @@
         <v>60</v>
       </c>
       <c r="K154" s="10">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="L154" s="10" t="s">
         <v>61</v>
@@ -11094,7 +11088,7 @@
         <v>79</v>
       </c>
       <c r="K155" s="10">
-        <v>184</v>
+        <v>138</v>
       </c>
       <c r="L155" s="10" t="s">
         <v>61</v>
@@ -11135,7 +11129,7 @@
         <v>68</v>
       </c>
       <c r="K156" s="10">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="L156" s="10" t="s">
         <v>61</v>
@@ -11176,7 +11170,7 @@
         <v>60</v>
       </c>
       <c r="K157" s="10">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="L157" s="10" t="s">
         <v>61</v>
@@ -11217,7 +11211,7 @@
         <v>60</v>
       </c>
       <c r="K158" s="10">
-        <v>207</v>
+        <v>109</v>
       </c>
       <c r="L158" s="10" t="s">
         <v>61</v>
@@ -11258,7 +11252,7 @@
         <v>68</v>
       </c>
       <c r="K159" s="10">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="L159" s="10" t="s">
         <v>61</v>
@@ -11299,7 +11293,7 @@
         <v>60</v>
       </c>
       <c r="K160" s="10">
-        <v>148</v>
+        <v>86</v>
       </c>
       <c r="L160" s="10" t="s">
         <v>61</v>
@@ -11340,7 +11334,7 @@
         <v>79</v>
       </c>
       <c r="K161" s="10">
-        <v>256</v>
+        <v>113</v>
       </c>
       <c r="L161" s="10" t="s">
         <v>61</v>
@@ -11381,7 +11375,7 @@
         <v>68</v>
       </c>
       <c r="K162" s="10">
-        <v>142</v>
+        <v>214</v>
       </c>
       <c r="L162" s="10" t="s">
         <v>61</v>
@@ -11422,7 +11416,7 @@
         <v>60</v>
       </c>
       <c r="K163" s="10">
-        <v>229</v>
+        <v>96</v>
       </c>
       <c r="L163" s="10" t="s">
         <v>61</v>
@@ -11463,7 +11457,7 @@
         <v>60</v>
       </c>
       <c r="K164" s="10">
-        <v>169</v>
+        <v>242</v>
       </c>
       <c r="L164" s="10" t="s">
         <v>61</v>
@@ -11504,7 +11498,7 @@
         <v>68</v>
       </c>
       <c r="K165" s="10">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="L165" s="10" t="s">
         <v>61</v>
@@ -11545,7 +11539,7 @@
         <v>60</v>
       </c>
       <c r="K166" s="10">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="L166" s="10" t="s">
         <v>61</v>
@@ -11586,7 +11580,7 @@
         <v>79</v>
       </c>
       <c r="K167" s="10">
-        <v>101</v>
+        <v>244</v>
       </c>
       <c r="L167" s="10" t="s">
         <v>61</v>
@@ -11627,7 +11621,7 @@
         <v>68</v>
       </c>
       <c r="K168" s="10">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L168" s="10" t="s">
         <v>61</v>
@@ -11668,7 +11662,7 @@
         <v>60</v>
       </c>
       <c r="K169" s="10">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L169" s="10" t="s">
         <v>61</v>
@@ -11709,7 +11703,7 @@
         <v>60</v>
       </c>
       <c r="K170" s="10">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="L170" s="10" t="s">
         <v>61</v>
@@ -11750,7 +11744,7 @@
         <v>68</v>
       </c>
       <c r="K171" s="10">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="L171" s="10" t="s">
         <v>61</v>
@@ -11791,7 +11785,7 @@
         <v>60</v>
       </c>
       <c r="K172" s="10">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="L172" s="10" t="s">
         <v>61</v>
@@ -11832,7 +11826,7 @@
         <v>79</v>
       </c>
       <c r="K173" s="10">
-        <v>116</v>
+        <v>252</v>
       </c>
       <c r="L173" s="10" t="s">
         <v>61</v>
@@ -11873,7 +11867,7 @@
         <v>68</v>
       </c>
       <c r="K174" s="10">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="L174" s="10" t="s">
         <v>61</v>
@@ -11914,7 +11908,7 @@
         <v>60</v>
       </c>
       <c r="K175" s="10">
-        <v>123</v>
+        <v>239</v>
       </c>
       <c r="L175" s="10" t="s">
         <v>61</v>
@@ -11955,7 +11949,7 @@
         <v>60</v>
       </c>
       <c r="K176" s="10">
-        <v>125</v>
+        <v>230</v>
       </c>
       <c r="L176" s="10" t="s">
         <v>61</v>
@@ -11996,7 +11990,7 @@
         <v>68</v>
       </c>
       <c r="K177" s="10">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="L177" s="10" t="s">
         <v>61</v>
@@ -12037,7 +12031,7 @@
         <v>60</v>
       </c>
       <c r="K178" s="10">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="L178" s="10" t="s">
         <v>61</v>
@@ -12078,7 +12072,7 @@
         <v>79</v>
       </c>
       <c r="K179" s="10">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="L179" s="10" t="s">
         <v>61</v>
@@ -12119,7 +12113,7 @@
         <v>68</v>
       </c>
       <c r="K180" s="10">
-        <v>115</v>
+        <v>238</v>
       </c>
       <c r="L180" s="10" t="s">
         <v>61</v>
@@ -12160,7 +12154,7 @@
         <v>60</v>
       </c>
       <c r="K181" s="10">
-        <v>225</v>
+        <v>99</v>
       </c>
       <c r="L181" s="10" t="s">
         <v>61</v>
@@ -12201,7 +12195,7 @@
         <v>60</v>
       </c>
       <c r="K182" s="10">
-        <v>196</v>
+        <v>137</v>
       </c>
       <c r="L182" s="10" t="s">
         <v>61</v>
@@ -12242,7 +12236,7 @@
         <v>68</v>
       </c>
       <c r="K183" s="10">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="L183" s="10" t="s">
         <v>61</v>
@@ -12283,7 +12277,7 @@
         <v>60</v>
       </c>
       <c r="K184" s="10">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="L184" s="10" t="s">
         <v>61</v>
@@ -12324,7 +12318,7 @@
         <v>79</v>
       </c>
       <c r="K185" s="10">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="L185" s="10" t="s">
         <v>61</v>
@@ -12365,7 +12359,7 @@
         <v>68</v>
       </c>
       <c r="K186" s="10">
-        <v>206</v>
+        <v>132</v>
       </c>
       <c r="L186" s="10" t="s">
         <v>61</v>
@@ -12406,7 +12400,7 @@
         <v>60</v>
       </c>
       <c r="K187" s="10">
-        <v>257</v>
+        <v>211</v>
       </c>
       <c r="L187" s="10" t="s">
         <v>61</v>
@@ -12447,7 +12441,7 @@
         <v>60</v>
       </c>
       <c r="K188" s="10">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="L188" s="10" t="s">
         <v>61</v>
@@ -12488,7 +12482,7 @@
         <v>68</v>
       </c>
       <c r="K189" s="10">
-        <v>253</v>
+        <v>103</v>
       </c>
       <c r="L189" s="10" t="s">
         <v>61</v>
@@ -12529,7 +12523,7 @@
         <v>60</v>
       </c>
       <c r="K190" s="10">
-        <v>196</v>
+        <v>155</v>
       </c>
       <c r="L190" s="10" t="s">
         <v>61</v>
@@ -12570,7 +12564,7 @@
         <v>79</v>
       </c>
       <c r="K191" s="10">
-        <v>257</v>
+        <v>189</v>
       </c>
       <c r="L191" s="10" t="s">
         <v>61</v>
@@ -12611,7 +12605,7 @@
         <v>68</v>
       </c>
       <c r="K192" s="10">
-        <v>152</v>
+        <v>247</v>
       </c>
       <c r="L192" s="10" t="s">
         <v>61</v>
@@ -12652,7 +12646,7 @@
         <v>60</v>
       </c>
       <c r="K193" s="10">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="L193" s="10" t="s">
         <v>61</v>
@@ -12693,7 +12687,7 @@
         <v>60</v>
       </c>
       <c r="K194" s="10">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="L194" s="10" t="s">
         <v>61</v>
@@ -12734,7 +12728,7 @@
         <v>68</v>
       </c>
       <c r="K195" s="10">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="L195" s="10" t="s">
         <v>61</v>
@@ -12775,7 +12769,7 @@
         <v>60</v>
       </c>
       <c r="K196" s="10">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="L196" s="10" t="s">
         <v>61</v>
@@ -12816,7 +12810,7 @@
         <v>79</v>
       </c>
       <c r="K197" s="10">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="L197" s="10" t="s">
         <v>61</v>
@@ -12857,7 +12851,7 @@
         <v>68</v>
       </c>
       <c r="K198" s="10">
-        <v>159</v>
+        <v>188</v>
       </c>
       <c r="L198" s="10" t="s">
         <v>61</v>
@@ -12898,7 +12892,7 @@
         <v>60</v>
       </c>
       <c r="K199" s="10">
-        <v>196</v>
+        <v>140</v>
       </c>
       <c r="L199" s="10" t="s">
         <v>61</v>
@@ -12939,7 +12933,7 @@
         <v>60</v>
       </c>
       <c r="K200" s="10">
-        <v>100</v>
+        <v>231</v>
       </c>
       <c r="L200" s="10" t="s">
         <v>61</v>
@@ -12980,7 +12974,7 @@
         <v>68</v>
       </c>
       <c r="K201" s="10">
-        <v>257</v>
+        <v>130</v>
       </c>
       <c r="L201" s="10" t="s">
         <v>61</v>
@@ -13021,7 +13015,7 @@
         <v>60</v>
       </c>
       <c r="K202" s="10">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="L202" s="10" t="s">
         <v>61</v>
@@ -13062,7 +13056,7 @@
         <v>79</v>
       </c>
       <c r="K203" s="10">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="L203" s="10" t="s">
         <v>61</v>
@@ -13103,7 +13097,7 @@
         <v>68</v>
       </c>
       <c r="K204" s="10">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="L204" s="10" t="s">
         <v>61</v>
@@ -13144,7 +13138,7 @@
         <v>60</v>
       </c>
       <c r="K205" s="10">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="L205" s="10" t="s">
         <v>61</v>
@@ -13185,7 +13179,7 @@
         <v>60</v>
       </c>
       <c r="K206" s="10">
-        <v>81</v>
+        <v>202</v>
       </c>
       <c r="L206" s="10" t="s">
         <v>61</v>
@@ -13226,7 +13220,7 @@
         <v>68</v>
       </c>
       <c r="K207" s="10">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="L207" s="10" t="s">
         <v>61</v>
@@ -13267,7 +13261,7 @@
         <v>60</v>
       </c>
       <c r="K208" s="10">
-        <v>210</v>
+        <v>113</v>
       </c>
       <c r="L208" s="10" t="s">
         <v>61</v>
@@ -13308,7 +13302,7 @@
         <v>79</v>
       </c>
       <c r="K209" s="10">
-        <v>156</v>
+        <v>230</v>
       </c>
       <c r="L209" s="10" t="s">
         <v>61</v>
@@ -13349,7 +13343,7 @@
         <v>68</v>
       </c>
       <c r="K210" s="10">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="L210" s="10" t="s">
         <v>61</v>
@@ -13390,7 +13384,7 @@
         <v>60</v>
       </c>
       <c r="K211" s="10">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="L211" s="10" t="s">
         <v>61</v>
@@ -13431,7 +13425,7 @@
         <v>60</v>
       </c>
       <c r="K212" s="10">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="L212" s="10" t="s">
         <v>61</v>
@@ -13472,7 +13466,7 @@
         <v>68</v>
       </c>
       <c r="K213" s="10">
-        <v>238</v>
+        <v>167</v>
       </c>
       <c r="L213" s="10" t="s">
         <v>61</v>
@@ -13513,7 +13507,7 @@
         <v>60</v>
       </c>
       <c r="K214" s="10">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="L214" s="10" t="s">
         <v>61</v>
@@ -13554,7 +13548,7 @@
         <v>79</v>
       </c>
       <c r="K215" s="10">
-        <v>248</v>
+        <v>180</v>
       </c>
       <c r="L215" s="10" t="s">
         <v>61</v>
@@ -13595,7 +13589,7 @@
         <v>68</v>
       </c>
       <c r="K216" s="10">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="L216" s="10" t="s">
         <v>61</v>
@@ -13636,7 +13630,7 @@
         <v>60</v>
       </c>
       <c r="K217" s="10">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="L217" s="10" t="s">
         <v>61</v>
@@ -13677,7 +13671,7 @@
         <v>60</v>
       </c>
       <c r="K218" s="10">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="L218" s="10" t="s">
         <v>61</v>
@@ -13718,7 +13712,7 @@
         <v>68</v>
       </c>
       <c r="K219" s="10">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="L219" s="10" t="s">
         <v>61</v>
@@ -13759,7 +13753,7 @@
         <v>60</v>
       </c>
       <c r="K220" s="10">
-        <v>169</v>
+        <v>119</v>
       </c>
       <c r="L220" s="10" t="s">
         <v>61</v>
@@ -13800,7 +13794,7 @@
         <v>79</v>
       </c>
       <c r="K221" s="10">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="L221" s="10" t="s">
         <v>61</v>
@@ -13841,7 +13835,7 @@
         <v>68</v>
       </c>
       <c r="K222" s="10">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="L222" s="10" t="s">
         <v>61</v>
@@ -13882,7 +13876,7 @@
         <v>60</v>
       </c>
       <c r="K223" s="10">
-        <v>258</v>
+        <v>125</v>
       </c>
       <c r="L223" s="10" t="s">
         <v>61</v>
@@ -13923,7 +13917,7 @@
         <v>60</v>
       </c>
       <c r="K224" s="10">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="L224" s="10" t="s">
         <v>61</v>
@@ -13964,7 +13958,7 @@
         <v>68</v>
       </c>
       <c r="K225" s="10">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="L225" s="10" t="s">
         <v>61</v>
@@ -14005,7 +13999,7 @@
         <v>60</v>
       </c>
       <c r="K226" s="10">
-        <v>132</v>
+        <v>206</v>
       </c>
       <c r="L226" s="10" t="s">
         <v>61</v>
@@ -14046,7 +14040,7 @@
         <v>79</v>
       </c>
       <c r="K227" s="10">
-        <v>138</v>
+        <v>240</v>
       </c>
       <c r="L227" s="10" t="s">
         <v>61</v>
@@ -14087,7 +14081,7 @@
         <v>68</v>
       </c>
       <c r="K228" s="10">
-        <v>112</v>
+        <v>224</v>
       </c>
       <c r="L228" s="10" t="s">
         <v>61</v>
@@ -14128,7 +14122,7 @@
         <v>60</v>
       </c>
       <c r="K229" s="10">
-        <v>207</v>
+        <v>103</v>
       </c>
       <c r="L229" s="10" t="s">
         <v>61</v>
@@ -14169,7 +14163,7 @@
         <v>60</v>
       </c>
       <c r="K230" s="10">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="L230" s="10" t="s">
         <v>61</v>
@@ -14210,7 +14204,7 @@
         <v>68</v>
       </c>
       <c r="K231" s="10">
-        <v>119</v>
+        <v>253</v>
       </c>
       <c r="L231" s="10" t="s">
         <v>61</v>
@@ -14251,7 +14245,7 @@
         <v>60</v>
       </c>
       <c r="K232" s="10">
-        <v>181</v>
+        <v>83</v>
       </c>
       <c r="L232" s="10" t="s">
         <v>61</v>
@@ -14292,7 +14286,7 @@
         <v>79</v>
       </c>
       <c r="K233" s="10">
-        <v>208</v>
+        <v>257</v>
       </c>
       <c r="L233" s="10" t="s">
         <v>61</v>
@@ -14333,7 +14327,7 @@
         <v>68</v>
       </c>
       <c r="K234" s="10">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="L234" s="10" t="s">
         <v>61</v>
@@ -14374,7 +14368,7 @@
         <v>60</v>
       </c>
       <c r="K235" s="10">
-        <v>213</v>
+        <v>166</v>
       </c>
       <c r="L235" s="10" t="s">
         <v>61</v>
@@ -14415,7 +14409,7 @@
         <v>60</v>
       </c>
       <c r="K236" s="10">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="L236" s="10" t="s">
         <v>61</v>
@@ -14456,7 +14450,7 @@
         <v>68</v>
       </c>
       <c r="K237" s="10">
-        <v>246</v>
+        <v>122</v>
       </c>
       <c r="L237" s="10" t="s">
         <v>61</v>
@@ -14497,7 +14491,7 @@
         <v>60</v>
       </c>
       <c r="K238" s="10">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="L238" s="10" t="s">
         <v>61</v>
@@ -14538,7 +14532,7 @@
         <v>79</v>
       </c>
       <c r="K239" s="10">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="L239" s="10" t="s">
         <v>61</v>
@@ -14579,7 +14573,7 @@
         <v>68</v>
       </c>
       <c r="K240" s="10">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L240" s="10" t="s">
         <v>61</v>
@@ -14620,7 +14614,7 @@
         <v>60</v>
       </c>
       <c r="K241" s="10">
-        <v>229</v>
+        <v>147</v>
       </c>
       <c r="L241" s="10" t="s">
         <v>61</v>
@@ -14661,7 +14655,7 @@
         <v>60</v>
       </c>
       <c r="K242" s="10">
-        <v>144</v>
+        <v>256</v>
       </c>
       <c r="L242" s="10" t="s">
         <v>61</v>
@@ -14702,7 +14696,7 @@
         <v>68</v>
       </c>
       <c r="K243" s="10">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="L243" s="10" t="s">
         <v>61</v>
@@ -14743,7 +14737,7 @@
         <v>60</v>
       </c>
       <c r="K244" s="10">
-        <v>141</v>
+        <v>244</v>
       </c>
       <c r="L244" s="10" t="s">
         <v>61</v>
@@ -14784,7 +14778,7 @@
         <v>79</v>
       </c>
       <c r="K245" s="10">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="L245" s="10" t="s">
         <v>61</v>
@@ -14825,7 +14819,7 @@
         <v>68</v>
       </c>
       <c r="K246" s="10">
-        <v>185</v>
+        <v>259</v>
       </c>
       <c r="L246" s="10" t="s">
         <v>61</v>
@@ -14866,7 +14860,7 @@
         <v>60</v>
       </c>
       <c r="K247" s="10">
-        <v>169</v>
+        <v>123</v>
       </c>
       <c r="L247" s="10" t="s">
         <v>61</v>
@@ -14907,7 +14901,7 @@
         <v>60</v>
       </c>
       <c r="K248" s="10">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L248" s="10" t="s">
         <v>61</v>
@@ -14948,7 +14942,7 @@
         <v>68</v>
       </c>
       <c r="K249" s="10">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="L249" s="10" t="s">
         <v>61</v>
@@ -14989,7 +14983,7 @@
         <v>60</v>
       </c>
       <c r="K250" s="10">
-        <v>254</v>
+        <v>84</v>
       </c>
       <c r="L250" s="10" t="s">
         <v>61</v>
@@ -15030,7 +15024,7 @@
         <v>79</v>
       </c>
       <c r="K251" s="10">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="L251" s="10" t="s">
         <v>61</v>
@@ -15071,7 +15065,7 @@
         <v>68</v>
       </c>
       <c r="K252" s="10">
-        <v>193</v>
+        <v>116</v>
       </c>
       <c r="L252" s="10" t="s">
         <v>61</v>
@@ -15112,7 +15106,7 @@
         <v>60</v>
       </c>
       <c r="K253" s="10">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="L253" s="10" t="s">
         <v>61</v>
@@ -15153,7 +15147,7 @@
         <v>60</v>
       </c>
       <c r="K254" s="10">
-        <v>180</v>
+        <v>243</v>
       </c>
       <c r="L254" s="10" t="s">
         <v>61</v>
@@ -15194,7 +15188,7 @@
         <v>68</v>
       </c>
       <c r="K255" s="10">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="L255" s="10" t="s">
         <v>61</v>
@@ -15235,7 +15229,7 @@
         <v>60</v>
       </c>
       <c r="K256" s="10">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="L256" s="10" t="s">
         <v>61</v>
@@ -15276,7 +15270,7 @@
         <v>79</v>
       </c>
       <c r="K257" s="10">
-        <v>175</v>
+        <v>126</v>
       </c>
       <c r="L257" s="10" t="s">
         <v>61</v>
@@ -15317,7 +15311,7 @@
         <v>68</v>
       </c>
       <c r="K258" s="10">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="L258" s="10" t="s">
         <v>61</v>
@@ -15358,7 +15352,7 @@
         <v>60</v>
       </c>
       <c r="K259" s="10">
-        <v>248</v>
+        <v>216</v>
       </c>
       <c r="L259" s="10" t="s">
         <v>61</v>
@@ -15399,7 +15393,7 @@
         <v>60</v>
       </c>
       <c r="K260" s="10">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="L260" s="10" t="s">
         <v>61</v>
@@ -15440,7 +15434,7 @@
         <v>68</v>
       </c>
       <c r="K261" s="10">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="L261" s="10" t="s">
         <v>61</v>
@@ -15481,7 +15475,7 @@
         <v>60</v>
       </c>
       <c r="K262" s="10">
-        <v>174</v>
+        <v>213</v>
       </c>
       <c r="L262" s="10" t="s">
         <v>61</v>
@@ -15522,7 +15516,7 @@
         <v>79</v>
       </c>
       <c r="K263" s="10">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="L263" s="10" t="s">
         <v>61</v>
@@ -15563,7 +15557,7 @@
         <v>68</v>
       </c>
       <c r="K264" s="10">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="L264" s="10" t="s">
         <v>61</v>
@@ -15604,7 +15598,7 @@
         <v>60</v>
       </c>
       <c r="K265" s="10">
-        <v>139</v>
+        <v>258</v>
       </c>
       <c r="L265" s="10" t="s">
         <v>61</v>
@@ -15645,7 +15639,7 @@
         <v>60</v>
       </c>
       <c r="K266" s="10">
-        <v>239</v>
+        <v>135</v>
       </c>
       <c r="L266" s="10" t="s">
         <v>61</v>
@@ -15686,7 +15680,7 @@
         <v>68</v>
       </c>
       <c r="K267" s="10">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="L267" s="10" t="s">
         <v>61</v>
@@ -15727,7 +15721,7 @@
         <v>60</v>
       </c>
       <c r="K268" s="10">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="L268" s="10" t="s">
         <v>61</v>
@@ -15768,7 +15762,7 @@
         <v>79</v>
       </c>
       <c r="K269" s="10">
-        <v>258</v>
+        <v>87</v>
       </c>
       <c r="L269" s="10" t="s">
         <v>61</v>
@@ -15809,7 +15803,7 @@
         <v>68</v>
       </c>
       <c r="K270" s="10">
-        <v>133</v>
+        <v>242</v>
       </c>
       <c r="L270" s="10" t="s">
         <v>61</v>
@@ -15850,7 +15844,7 @@
         <v>60</v>
       </c>
       <c r="K271" s="10">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="L271" s="10" t="s">
         <v>61</v>
@@ -15891,7 +15885,7 @@
         <v>60</v>
       </c>
       <c r="K272" s="10">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="L272" s="10" t="s">
         <v>61</v>
@@ -15932,7 +15926,7 @@
         <v>68</v>
       </c>
       <c r="K273" s="10">
-        <v>146</v>
+        <v>92</v>
       </c>
       <c r="L273" s="10" t="s">
         <v>61</v>
@@ -15973,7 +15967,7 @@
         <v>60</v>
       </c>
       <c r="K274" s="10">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="L274" s="10" t="s">
         <v>61</v>
@@ -16014,7 +16008,7 @@
         <v>79</v>
       </c>
       <c r="K275" s="10">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="L275" s="10" t="s">
         <v>61</v>
@@ -16055,7 +16049,7 @@
         <v>68</v>
       </c>
       <c r="K276" s="10">
-        <v>251</v>
+        <v>202</v>
       </c>
       <c r="L276" s="10" t="s">
         <v>61</v>
@@ -16096,7 +16090,7 @@
         <v>60</v>
       </c>
       <c r="K277" s="10">
-        <v>85</v>
+        <v>134</v>
       </c>
       <c r="L277" s="10" t="s">
         <v>61</v>
@@ -16137,7 +16131,7 @@
         <v>60</v>
       </c>
       <c r="K278" s="10">
-        <v>187</v>
+        <v>114</v>
       </c>
       <c r="L278" s="10" t="s">
         <v>61</v>
@@ -16178,7 +16172,7 @@
         <v>68</v>
       </c>
       <c r="K279" s="10">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="L279" s="10" t="s">
         <v>61</v>
@@ -16219,7 +16213,7 @@
         <v>60</v>
       </c>
       <c r="K280" s="10">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="L280" s="10" t="s">
         <v>61</v>
@@ -16260,7 +16254,7 @@
         <v>79</v>
       </c>
       <c r="K281" s="10">
-        <v>105</v>
+        <v>240</v>
       </c>
       <c r="L281" s="10" t="s">
         <v>61</v>
@@ -16301,7 +16295,7 @@
         <v>68</v>
       </c>
       <c r="K282" s="10">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="L282" s="10" t="s">
         <v>61</v>
@@ -16342,7 +16336,7 @@
         <v>60</v>
       </c>
       <c r="K283" s="10">
-        <v>176</v>
+        <v>105</v>
       </c>
       <c r="L283" s="10" t="s">
         <v>61</v>
@@ -16383,7 +16377,7 @@
         <v>60</v>
       </c>
       <c r="K284" s="10">
-        <v>103</v>
+        <v>252</v>
       </c>
       <c r="L284" s="10" t="s">
         <v>61</v>
@@ -16424,7 +16418,7 @@
         <v>68</v>
       </c>
       <c r="K285" s="10">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="L285" s="10" t="s">
         <v>61</v>
@@ -16465,7 +16459,7 @@
         <v>60</v>
       </c>
       <c r="K286" s="10">
-        <v>190</v>
+        <v>104</v>
       </c>
       <c r="L286" s="10" t="s">
         <v>61</v>
@@ -16506,7 +16500,7 @@
         <v>79</v>
       </c>
       <c r="K287" s="10">
-        <v>146</v>
+        <v>249</v>
       </c>
       <c r="L287" s="10" t="s">
         <v>61</v>
@@ -16547,7 +16541,7 @@
         <v>68</v>
       </c>
       <c r="K288" s="10">
-        <v>253</v>
+        <v>129</v>
       </c>
       <c r="L288" s="10" t="s">
         <v>61</v>
@@ -16588,7 +16582,7 @@
         <v>60</v>
       </c>
       <c r="K289" s="10">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="L289" s="10" t="s">
         <v>61</v>
@@ -16629,7 +16623,7 @@
         <v>60</v>
       </c>
       <c r="K290" s="10">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="L290" s="10" t="s">
         <v>61</v>
@@ -16670,7 +16664,7 @@
         <v>68</v>
       </c>
       <c r="K291" s="10">
-        <v>189</v>
+        <v>227</v>
       </c>
       <c r="L291" s="10" t="s">
         <v>61</v>
@@ -16711,7 +16705,7 @@
         <v>60</v>
       </c>
       <c r="K292" s="10">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="L292" s="10" t="s">
         <v>61</v>
@@ -16752,7 +16746,7 @@
         <v>79</v>
       </c>
       <c r="K293" s="10">
-        <v>189</v>
+        <v>83</v>
       </c>
       <c r="L293" s="10" t="s">
         <v>61</v>
@@ -16793,7 +16787,7 @@
         <v>68</v>
       </c>
       <c r="K294" s="10">
-        <v>154</v>
+        <v>225</v>
       </c>
       <c r="L294" s="10" t="s">
         <v>61</v>
@@ -16834,7 +16828,7 @@
         <v>60</v>
       </c>
       <c r="K295" s="10">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="L295" s="10" t="s">
         <v>61</v>
@@ -16875,7 +16869,7 @@
         <v>60</v>
       </c>
       <c r="K296" s="10">
-        <v>164</v>
+        <v>257</v>
       </c>
       <c r="L296" s="10" t="s">
         <v>61</v>
@@ -16916,7 +16910,7 @@
         <v>68</v>
       </c>
       <c r="K297" s="10">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="L297" s="10" t="s">
         <v>61</v>
@@ -16957,7 +16951,7 @@
         <v>60</v>
       </c>
       <c r="K298" s="10">
-        <v>122</v>
+        <v>186</v>
       </c>
       <c r="L298" s="10" t="s">
         <v>61</v>
@@ -16998,7 +16992,7 @@
         <v>79</v>
       </c>
       <c r="K299" s="10">
-        <v>113</v>
+        <v>239</v>
       </c>
       <c r="L299" s="10" t="s">
         <v>61</v>
@@ -17039,7 +17033,7 @@
         <v>68</v>
       </c>
       <c r="K300" s="10">
-        <v>163</v>
+        <v>226</v>
       </c>
       <c r="L300" s="10" t="s">
         <v>61</v>
@@ -17080,7 +17074,7 @@
         <v>60</v>
       </c>
       <c r="K301" s="10">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="L301" s="10" t="s">
         <v>61</v>
@@ -17358,7 +17352,7 @@
         <v>1129</v>
       </c>
       <c r="H308" s="10" t="s">
-        <v>1160</v>
+        <v>1150</v>
       </c>
       <c r="I308" s="11" t="s">
         <v>11</v>
@@ -17378,7 +17372,7 @@
     </row>
     <row r="309" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="10" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B309" s="10" t="s">
         <v>53</v>
@@ -17387,19 +17381,19 @@
         <v>1125</v>
       </c>
       <c r="D309" s="10" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E309" s="10" t="s">
         <v>1162</v>
       </c>
-      <c r="E309" s="10" t="s">
+      <c r="F309" s="10" t="s">
         <v>1163</v>
-      </c>
-      <c r="F309" s="10" t="s">
-        <v>1164</v>
       </c>
       <c r="G309" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H309" s="10" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="I309" s="11" t="s">
         <v>11</v>
@@ -17419,7 +17413,7 @@
     </row>
     <row r="310" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="10" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B310" s="10" t="s">
         <v>53</v>
@@ -17428,19 +17422,19 @@
         <v>1125</v>
       </c>
       <c r="D310" s="10" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E310" s="10" t="s">
         <v>1167</v>
       </c>
-      <c r="E310" s="10" t="s">
+      <c r="F310" s="10" t="s">
         <v>1168</v>
-      </c>
-      <c r="F310" s="10" t="s">
-        <v>1169</v>
       </c>
       <c r="G310" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H310" s="10" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="I310" s="11" t="s">
         <v>11</v>
@@ -17460,7 +17454,7 @@
     </row>
     <row r="311" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="10" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B311" s="10" t="s">
         <v>53</v>
@@ -17469,19 +17463,19 @@
         <v>1125</v>
       </c>
       <c r="D311" s="10" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E311" s="10" t="s">
         <v>1172</v>
       </c>
-      <c r="E311" s="10" t="s">
+      <c r="F311" s="10" t="s">
         <v>1173</v>
-      </c>
-      <c r="F311" s="10" t="s">
-        <v>1174</v>
       </c>
       <c r="G311" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H311" s="10" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="I311" s="11" t="s">
         <v>11</v>
@@ -17501,7 +17495,7 @@
     </row>
     <row r="312" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="10" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B312" s="10" t="s">
         <v>53</v>
@@ -17510,19 +17504,19 @@
         <v>1125</v>
       </c>
       <c r="D312" s="10" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E312" s="10" t="s">
         <v>1177</v>
       </c>
-      <c r="E312" s="10" t="s">
+      <c r="F312" s="10" t="s">
         <v>1178</v>
-      </c>
-      <c r="F312" s="10" t="s">
-        <v>1179</v>
       </c>
       <c r="G312" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H312" s="10" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="I312" s="11" t="s">
         <v>11</v>
@@ -17542,7 +17536,7 @@
     </row>
     <row r="313" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="10" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B313" s="10" t="s">
         <v>53</v>
@@ -17551,19 +17545,19 @@
         <v>1125</v>
       </c>
       <c r="D313" s="10" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E313" s="10" t="s">
         <v>1182</v>
       </c>
-      <c r="E313" s="10" t="s">
+      <c r="F313" s="10" t="s">
         <v>1183</v>
-      </c>
-      <c r="F313" s="10" t="s">
-        <v>1184</v>
       </c>
       <c r="G313" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H313" s="10" t="s">
-        <v>1185</v>
+        <v>1140</v>
       </c>
       <c r="I313" s="11" t="s">
         <v>11</v>
@@ -17583,7 +17577,7 @@
     </row>
     <row r="314" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="10" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="B314" s="10" t="s">
         <v>53</v>
@@ -17592,19 +17586,19 @@
         <v>1125</v>
       </c>
       <c r="D314" s="10" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E314" s="10" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F314" s="10" t="s">
         <v>1187</v>
-      </c>
-      <c r="E314" s="10" t="s">
-        <v>1188</v>
-      </c>
-      <c r="F314" s="10" t="s">
-        <v>1189</v>
       </c>
       <c r="G314" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H314" s="10" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="I314" s="11" t="s">
         <v>11</v>
@@ -17624,7 +17618,7 @@
     </row>
     <row r="315" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A315" s="10" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="B315" s="10" t="s">
         <v>53</v>
@@ -17633,19 +17627,19 @@
         <v>1125</v>
       </c>
       <c r="D315" s="10" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E315" s="10" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F315" s="10" t="s">
         <v>1192</v>
-      </c>
-      <c r="E315" s="10" t="s">
-        <v>1193</v>
-      </c>
-      <c r="F315" s="10" t="s">
-        <v>1194</v>
       </c>
       <c r="G315" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H315" s="10" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="I315" s="11" t="s">
         <v>11</v>
@@ -17665,7 +17659,7 @@
     </row>
     <row r="316" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A316" s="10" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B316" s="10" t="s">
         <v>53</v>
@@ -17674,19 +17668,19 @@
         <v>1125</v>
       </c>
       <c r="D316" s="10" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E316" s="10" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F316" s="10" t="s">
         <v>1197</v>
-      </c>
-      <c r="E316" s="10" t="s">
-        <v>1198</v>
-      </c>
-      <c r="F316" s="10" t="s">
-        <v>1199</v>
       </c>
       <c r="G316" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H316" s="10" t="s">
-        <v>1130</v>
+        <v>1198</v>
       </c>
       <c r="I316" s="11" t="s">
         <v>11</v>
@@ -17706,7 +17700,7 @@
     </row>
     <row r="317" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="10" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B317" s="10" t="s">
         <v>53</v>
@@ -17715,19 +17709,19 @@
         <v>1125</v>
       </c>
       <c r="D317" s="10" t="s">
-        <v>1201</v>
+        <v>1176</v>
       </c>
       <c r="E317" s="10" t="s">
-        <v>1202</v>
+        <v>1177</v>
       </c>
       <c r="F317" s="10" t="s">
-        <v>1203</v>
+        <v>1178</v>
       </c>
       <c r="G317" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H317" s="10" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="I317" s="11" t="s">
         <v>11</v>
@@ -17747,7 +17741,7 @@
     </row>
     <row r="318" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A318" s="10" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="B318" s="10" t="s">
         <v>53</v>
@@ -17756,19 +17750,19 @@
         <v>1125</v>
       </c>
       <c r="D318" s="10" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="E318" s="10" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="F318" s="10" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="G318" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H318" s="10" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="I318" s="11" t="s">
         <v>11</v>
@@ -17788,7 +17782,7 @@
     </row>
     <row r="319" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="10" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="B319" s="10" t="s">
         <v>53</v>
@@ -17797,19 +17791,19 @@
         <v>1125</v>
       </c>
       <c r="D319" s="10" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="E319" s="10" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="F319" s="10" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="G319" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H319" s="10" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="I319" s="11" t="s">
         <v>11</v>
@@ -17829,7 +17823,7 @@
     </row>
     <row r="320" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="10" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="B320" s="10" t="s">
         <v>53</v>
@@ -17838,19 +17832,19 @@
         <v>1125</v>
       </c>
       <c r="D320" s="10" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="E320" s="10" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="F320" s="10" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="G320" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H320" s="10" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="I320" s="11" t="s">
         <v>11</v>
@@ -17870,7 +17864,7 @@
     </row>
     <row r="321" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="10" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="B321" s="10" t="s">
         <v>53</v>
@@ -17879,19 +17873,19 @@
         <v>1125</v>
       </c>
       <c r="D321" s="10" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="E321" s="10" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="F321" s="10" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="G321" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H321" s="10" t="s">
-        <v>1224</v>
+        <v>1215</v>
       </c>
       <c r="I321" s="11" t="s">
         <v>11</v>
@@ -17911,7 +17905,7 @@
     </row>
     <row r="322" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="10" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="B322" s="10" t="s">
         <v>53</v>
@@ -17920,19 +17914,19 @@
         <v>1125</v>
       </c>
       <c r="D322" s="10" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="E322" s="10" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="F322" s="10" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="G322" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H322" s="10" t="s">
-        <v>1155</v>
+        <v>1224</v>
       </c>
       <c r="I322" s="11" t="s">
         <v>11</v>
@@ -17952,7 +17946,7 @@
     </row>
     <row r="323" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="10" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="B323" s="10" t="s">
         <v>53</v>
@@ -17961,19 +17955,19 @@
         <v>1125</v>
       </c>
       <c r="D323" s="10" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="E323" s="10" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="F323" s="10" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="G323" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H323" s="10" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="I323" s="11" t="s">
         <v>11</v>
@@ -17993,7 +17987,7 @@
     </row>
     <row r="324" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="10" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="B324" s="10" t="s">
         <v>53</v>
@@ -18002,19 +17996,19 @@
         <v>1125</v>
       </c>
       <c r="D324" s="10" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="E324" s="10" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="F324" s="10" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="G324" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H324" s="10" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="I324" s="11" t="s">
         <v>11</v>
@@ -18034,7 +18028,7 @@
     </row>
     <row r="325" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="10" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B325" s="10" t="s">
         <v>53</v>
@@ -18043,19 +18037,19 @@
         <v>1125</v>
       </c>
       <c r="D325" s="10" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="E325" s="10" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="F325" s="10" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="G325" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H325" s="10" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="I325" s="11" t="s">
         <v>11</v>
@@ -18075,7 +18069,7 @@
     </row>
     <row r="326" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="10" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="B326" s="10" t="s">
         <v>53</v>
@@ -18084,19 +18078,19 @@
         <v>1125</v>
       </c>
       <c r="D326" s="10" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="E326" s="10" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="F326" s="10" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="G326" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H326" s="10" t="s">
-        <v>1140</v>
+        <v>1244</v>
       </c>
       <c r="I326" s="11" t="s">
         <v>11</v>
@@ -18116,7 +18110,7 @@
     </row>
     <row r="327" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="10" t="s">
-        <v>1248</v>
+        <v>1245</v>
       </c>
       <c r="B327" s="10" t="s">
         <v>53</v>
@@ -18125,19 +18119,19 @@
         <v>1125</v>
       </c>
       <c r="D327" s="10" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="E327" s="10" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="F327" s="10" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="G327" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H327" s="10" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="I327" s="11" t="s">
         <v>11</v>
@@ -18157,7 +18151,7 @@
     </row>
     <row r="328" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="10" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="B328" s="10" t="s">
         <v>53</v>
@@ -18166,19 +18160,19 @@
         <v>1125</v>
       </c>
       <c r="D328" s="10" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="E328" s="10" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="F328" s="10" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="G328" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H328" s="10" t="s">
-        <v>1257</v>
+        <v>1215</v>
       </c>
       <c r="I328" s="11" t="s">
         <v>11</v>
@@ -18198,7 +18192,7 @@
     </row>
     <row r="329" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="10" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="B329" s="10" t="s">
         <v>53</v>
@@ -18207,19 +18201,19 @@
         <v>1125</v>
       </c>
       <c r="D329" s="10" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="E329" s="10" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="F329" s="10" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="G329" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H329" s="10" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="I329" s="11" t="s">
         <v>11</v>
@@ -18239,7 +18233,7 @@
     </row>
     <row r="330" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="10" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="B330" s="10" t="s">
         <v>53</v>
@@ -18248,19 +18242,19 @@
         <v>1125</v>
       </c>
       <c r="D330" s="10" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="E330" s="10" t="s">
-        <v>1207</v>
+        <v>1261</v>
       </c>
       <c r="F330" s="10" t="s">
-        <v>1208</v>
+        <v>1262</v>
       </c>
       <c r="G330" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H330" s="10" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="I330" s="11" t="s">
         <v>11</v>
@@ -18280,7 +18274,7 @@
     </row>
     <row r="331" ht="36" customHeight="1" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="10" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B331" s="10" t="s">
         <v>53</v>
@@ -18289,19 +18283,19 @@
         <v>1125</v>
       </c>
       <c r="D331" s="10" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E331" s="10" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F331" s="10" t="s">
         <v>1267</v>
-      </c>
-      <c r="E331" s="10" t="s">
-        <v>1268</v>
-      </c>
-      <c r="F331" s="10" t="s">
-        <v>1269</v>
       </c>
       <c r="G331" s="10" t="s">
         <v>1129</v>
       </c>
       <c r="H331" s="10" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="I331" s="11" t="s">
         <v>11</v>
